--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="jWsVDqksBr4MxBklPR3eXLh4dzZXBcIsXm68HYjaGSM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sRwcLHFO/e2p7cfFFBUEUHbIbm61vZrCZyYcbfcMveg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="303">
   <si>
     <t>ID</t>
   </si>
@@ -144,15 +144,27 @@
     <t>TC006</t>
   </si>
   <si>
+    <t>Переход со страницы Main на  About</t>
+  </si>
+  <si>
+    <t>1. Нажать кнопку бокового меню (шторка, верхний левый угол)</t>
+  </si>
+  <si>
+    <t>1. Меню открывается, кнопки News и About активны</t>
+  </si>
+  <si>
+    <t>2. Нажать кнопку About</t>
+  </si>
+  <si>
+    <t>2. Пользователь переходит на страницу About</t>
+  </si>
+  <si>
+    <t>TC007</t>
+  </si>
+  <si>
     <t>Переход со страницы Main на News, потом с News на About</t>
   </si>
   <si>
-    <t>1. Нажать кнопку бокового меню (шторка, верхний левый угол)</t>
-  </si>
-  <si>
-    <t>1. Меню открывается, кнопки News и About активны</t>
-  </si>
-  <si>
     <t>2. Нажать кнопку News</t>
   </si>
   <si>
@@ -171,7 +183,7 @@
     <t>4. Пользователь переходит на страницу About</t>
   </si>
   <si>
-    <t>TC007</t>
+    <t>TC008</t>
   </si>
   <si>
     <t>Переход со страницы News на страницу Main при нажатии системной кнопки "Назад"</t>
@@ -186,10 +198,10 @@
     <t>1. Пользователь переходит на страницу Main</t>
   </si>
   <si>
-    <t>TC008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Однократное нажатие системной кнопки "Назад" на главной странице Main </t>
+    <t>TC009</t>
+  </si>
+  <si>
+    <t>Однократное нажатие системной кнопки "Назад" на главной странице Main сворачивает приложение</t>
   </si>
   <si>
     <t>Low</t>
@@ -201,7 +213,7 @@
     <t>1. Пользователь остается на страницу Main, приложение не закрывается</t>
   </si>
   <si>
-    <t>TC009</t>
+    <t>TC0010</t>
   </si>
   <si>
     <t>Поворот экрана на странице Main</t>
@@ -216,6 +228,9 @@
     <t>1.Все элементы отображаются корректно, читаемы, не наезжают друг на друга, не обрезаются.</t>
   </si>
   <si>
+    <t>Не подлежит автоматизации, т.к. требуется проверка не только доступности и отображения элементов, но и конкретное расположение их на экране разных устройств, что затруднительно реализовать, тесты будут нестабильны и трудноподдерживаемы.</t>
+  </si>
+  <si>
     <t>2. Повернуть устройство/эмулятор в горизонтальный режим (landscape)</t>
   </si>
   <si>
@@ -240,7 +255,7 @@
     <t>5. После возврата в вертикальный режим расположение элементов восстановилось к исходному (как на шаге 1). Список новостей и скролл не сбросились (если это не противоречит логике).</t>
   </si>
   <si>
-    <t>TC010</t>
+    <t>TC011</t>
   </si>
   <si>
     <t>Новость содержит заголовок, дату, категорию, комментарий</t>
@@ -267,7 +282,7 @@
     <t>3. Открывается комментарий</t>
   </si>
   <si>
-    <t>TC011</t>
+    <t>TC012</t>
   </si>
   <si>
     <t>Создание новости со всеми заполнеными полями</t>
@@ -336,7 +351,7 @@
     <t xml:space="preserve">10. Новость создается и отображается в списке </t>
   </si>
   <si>
-    <t>TC012</t>
+    <t>TC013</t>
   </si>
   <si>
     <t>Нажатие кнопки "Cancel" вместо "Save" при создании новости</t>
@@ -354,7 +369,7 @@
     <t>10. Новость не создается, пользователь остается на странице редактирования новостей</t>
   </si>
   <si>
-    <t>TC013</t>
+    <t>TC014</t>
   </si>
   <si>
     <t>Нажатие кнопки "Ok" при удалении новости</t>
@@ -366,28 +381,31 @@
     <t>2. Нажать кнопку "Delete" (корзина)</t>
   </si>
   <si>
+    <t>2. Появляется сообщение "Are you sure you want to permanently delete the document? These changes cannot be reversed in the future. "</t>
+  </si>
+  <si>
+    <t>3. Нажать "Ok"</t>
+  </si>
+  <si>
+    <t>3. Новость удаляется, пользователь остается на странице редактирования новостей</t>
+  </si>
+  <si>
+    <t>TC015</t>
+  </si>
+  <si>
+    <t>Нажатие кнопки "Cancel" при удалении новости</t>
+  </si>
+  <si>
     <t>2. Появляется сообщение "Are you sure you want to permanently delete the document? These changes cannot be reversed in the future? "</t>
   </si>
   <si>
-    <t>3. Нажать "Ok"</t>
-  </si>
-  <si>
-    <t>3. Новость удаляется, пользователь остается на странице редактирования новостей</t>
-  </si>
-  <si>
-    <t>TC014</t>
-  </si>
-  <si>
-    <t>Нажатие кнопки "Cancel" при удалении новости</t>
-  </si>
-  <si>
     <t>3. Нажать "Cancel"</t>
   </si>
   <si>
     <t>3. Новость не удаляется, пользователь остается на странице редактирования новостей</t>
   </si>
   <si>
-    <t>TC015</t>
+    <t>TC016</t>
   </si>
   <si>
     <t>Фильтрация новостей за сегодня</t>
@@ -436,7 +454,7 @@
     <t>5. Отображаются новости за сегодня</t>
   </si>
   <si>
-    <t>TC016</t>
+    <t>TC017</t>
   </si>
   <si>
     <t>Фильтрация новостей за неделю</t>
@@ -510,7 +528,7 @@
     <t>8. Отображаются новости за неделю</t>
   </si>
   <si>
-    <t>TC017</t>
+    <t>TC018</t>
   </si>
   <si>
     <t>Фильтрация новостей за месяц</t>
@@ -569,7 +587,7 @@
     <t>8. Отображаются новости за месяц</t>
   </si>
   <si>
-    <t>TC018</t>
+    <t>TC019</t>
   </si>
   <si>
     <t>Фильтрация новостей по категории "Объявление"</t>
@@ -587,7 +605,7 @@
     <t>5. Отображаются новости только с категорией "Объявление"</t>
   </si>
   <si>
-    <t>TC019</t>
+    <t>TC020</t>
   </si>
   <si>
     <t>Фильтрация новостей по категории "Массаж" и дата сегодня</t>
@@ -624,7 +642,7 @@
     <t xml:space="preserve">5. Отображаются только новости за сегодня с категорией "Массаж" </t>
   </si>
   <si>
-    <t>TC020</t>
+    <t>TC021</t>
   </si>
   <si>
     <t>Сброс фильтра по умолчанию - показываются все новости</t>
@@ -645,7 +663,7 @@
     <t>4. Отображаются все новости</t>
   </si>
   <si>
-    <t>TC021</t>
+    <t>TC022</t>
   </si>
   <si>
     <t>Дата создания ("Creation date") новости равна дате публикации ("Publication date")</t>
@@ -660,7 +678,7 @@
     <t>2. Даты идентичны</t>
   </si>
   <si>
-    <t>TC022</t>
+    <t>TC023</t>
   </si>
   <si>
     <t xml:space="preserve">Дата публикации ("Publication date") новости равна завтрашней дате </t>
@@ -672,7 +690,7 @@
     <t>2. Сравнить "Publication date" с завтрашней датой</t>
   </si>
   <si>
-    <t>TC023</t>
+    <t>TC024</t>
   </si>
   <si>
     <t>Переход на страницу "Цитаты"</t>
@@ -690,7 +708,7 @@
     <t>2. Текст совпадает с "Хоспис для меня - это то, каким должен быть мир."</t>
   </si>
   <si>
-    <t>TC024</t>
+    <t>TC025</t>
   </si>
   <si>
     <t>Развернуть первую цитату</t>
@@ -711,7 +729,7 @@
     <t>2. Пользователь видит текст: "Ну, идеальное устройство мира в моих глазах. Где никто не оценивает, никто не осудит, где говоришь, и тебяслышат, где, если страшно, тебя обнимут и возьмут за руку, а если холодно тебя согреют". Юлия Капис, волонтер</t>
   </si>
   <si>
-    <t>TC025</t>
+    <t>TC026</t>
   </si>
   <si>
     <t>Свернуть первую цитату</t>
@@ -729,7 +747,7 @@
     <t>2. Циата сворачивается, виден только текст "Хоспис для меня - это то, каким должен быть мир."</t>
   </si>
   <si>
-    <t>TC026</t>
+    <t>TC027</t>
   </si>
   <si>
     <t>Переход на страницу About</t>
@@ -738,13 +756,7 @@
     <t>1. Меню открывается, кнопка About активна</t>
   </si>
   <si>
-    <t>2. Нажать кнопку About</t>
-  </si>
-  <si>
-    <t>2. Пользователь переходит на страницу About</t>
-  </si>
-  <si>
-    <t>TC027</t>
+    <t>TC028</t>
   </si>
   <si>
     <t>Переход по ссылке «Политика конфиденциальности» (Privacy Policy)</t>
@@ -760,7 +772,7 @@
     <t>1. Открывается браузер, страница загружается без ошибок</t>
   </si>
   <si>
-    <t>TC028</t>
+    <t>TC029</t>
   </si>
   <si>
     <t>Переход по ссылке «Пользовательское соглашение» (Terms of Use)</t>
@@ -769,7 +781,7 @@
     <t>1. Нажать на ссылку https;//vhospice.org/#/terms-of-use/</t>
   </si>
   <si>
-    <t>TC029</t>
+    <t>TC030</t>
   </si>
   <si>
     <t>Сообщение "No internet" при переходе по ссылке «Политика конфиденциальности» (Privacy Policy) c отключенным Wi-Fi и мобильными данными.</t>
@@ -793,7 +805,7 @@
     <t>3. Появляется сообщение "No internet", приложение не крашится, Chrome не виснет и не падает</t>
   </si>
   <si>
-    <t>TC030</t>
+    <t>TC031</t>
   </si>
   <si>
     <t>Сообщение "No internet" при переходе по ссылке «Пользовательское соглашение» (Terms of Use) c отключенным Wi-Fi и мобильными данными.</t>
@@ -802,7 +814,7 @@
     <t>3. Нажать на ссылку https;//vhospice.org/#/terms-of-use/</t>
   </si>
   <si>
-    <t>TC031</t>
+    <t>TC032</t>
   </si>
   <si>
     <t>Сообщение "No internet" при отключении Wi-Fi и мобильных данных на главной странице Main и переход на страницу News</t>
@@ -821,7 +833,7 @@
     <t>4. Пользователь переходит на страницу News, получает сообщение No internet.</t>
   </si>
   <si>
-    <t>TC032</t>
+    <t>TC033</t>
   </si>
   <si>
     <t>Включение Wi-Fi и мобильных данных на главной странице Main</t>
@@ -840,7 +852,7 @@
     <t>4. Пользователь переходит на страницу News, ошибок нет</t>
   </si>
   <si>
-    <t>TC033</t>
+    <t>TC034</t>
   </si>
   <si>
     <t>Нельзя выбрать вчерашнюю дату при создании новости</t>
@@ -861,7 +873,7 @@
     <t>2. Дата неактивна</t>
   </si>
   <si>
-    <t>TC034</t>
+    <t>TC035</t>
   </si>
   <si>
     <t xml:space="preserve">Создание новости с пустым полем Category </t>
@@ -897,7 +909,7 @@
     <t>8. Новость не создается, появляется ошибка "Fill empty fields"</t>
   </si>
   <si>
-    <t>TC035</t>
+    <t>TC036</t>
   </si>
   <si>
     <t xml:space="preserve">Создание новости с пустым полем Description </t>
@@ -912,7 +924,7 @@
     <t>7. Поле остается пустым</t>
   </si>
   <si>
-    <t>TC036</t>
+    <t>TC037</t>
   </si>
   <si>
     <t>Создание новости с пустым полем Publication date</t>
@@ -939,7 +951,7 @@
     <t>7. Новость не создается, появляется ошибка "Fill empty fields"</t>
   </si>
   <si>
-    <t>TC037</t>
+    <t>TC038</t>
   </si>
   <si>
     <t>Создание новости с пустым полем Time</t>
@@ -954,7 +966,7 @@
     <t>5. Поле остается пустым</t>
   </si>
   <si>
-    <t>TC038</t>
+    <t>TC039</t>
   </si>
   <si>
     <t>Создание новости с пустым полем Title</t>
@@ -963,7 +975,7 @@
     <t>2. В поле "Title" ничего не вводить - оставить пустым</t>
   </si>
   <si>
-    <t>TC039</t>
+    <t>TC040</t>
   </si>
   <si>
     <t>Создание новости со всеми пустыми полями</t>
@@ -984,7 +996,7 @@
     <t>6. Новость не создается, появляется ошибка "Fill empty fields"</t>
   </si>
   <si>
-    <t>TC040</t>
+    <t>TC041</t>
   </si>
   <si>
     <t>Создание новости с заголовком в поле Title длиной 50+ символов</t>
@@ -1002,7 +1014,7 @@
     <t>8. Новость создается</t>
   </si>
   <si>
-    <t>TC041</t>
+    <t>TC042</t>
   </si>
   <si>
     <t>Создание новости с внедрением HTML-тегов (XSS-попытка) во всех текстовых полях</t>
@@ -1017,7 +1029,7 @@
     <t>8. Новость не создается, ошибка "Saving failed. Try again later"</t>
   </si>
   <si>
-    <t>TC042</t>
+    <t>TC043</t>
   </si>
   <si>
     <t>Сортировка новостей по дате (от новых к старым)</t>
@@ -1165,7 +1177,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1202,7 +1214,9 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1223,7 +1237,12 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1233,6 +1252,8 @@
     <xf borderId="2" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1507,7 +1528,9 @@
       <c r="G2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="12"/>
+      <c r="H2" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13"/>
@@ -1559,7 +1582,9 @@
       <c r="G5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13"/>
@@ -1611,7 +1636,9 @@
       <c r="G8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13"/>
@@ -1663,7 +1690,9 @@
       <c r="G11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13"/>
@@ -1715,7 +1744,9 @@
       <c r="G14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="12"/>
+      <c r="H14" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14"/>
@@ -1753,149 +1784,169 @@
       <c r="G16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="12"/>
+      <c r="H16" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
       <c r="F17" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="13"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="18">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F18" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="13"/>
+        <v>44</v>
+      </c>
+      <c r="H18" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="14"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="G20" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="21"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="18" t="s">
+      <c r="E22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="F22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D23" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" s="21"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="G23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" s="12"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="11" t="s">
+      <c r="E24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H23" s="13"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
       <c r="F24" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="H24" s="13"/>
+      <c r="H24" s="22" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13"/>
@@ -1904,130 +1955,134 @@
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H25" s="13"/>
     </row>
     <row r="26">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="H26" s="14"/>
+        <v>74</v>
+      </c>
+      <c r="H26" s="13"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="G27" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H27" s="12"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
+      <c r="E29" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="F29" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="14"/>
+        <v>83</v>
+      </c>
+      <c r="H29" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="G30" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H30" s="13"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D32" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="12"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="13"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="E32" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="F32" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="H32" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H32" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13"/>
@@ -2036,10 +2091,10 @@
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H33" s="13"/>
     </row>
@@ -2050,10 +2105,10 @@
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
       <c r="F34" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H34" s="13"/>
     </row>
@@ -2064,10 +2119,10 @@
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
       <c r="F35" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H35" s="13"/>
     </row>
@@ -2078,10 +2133,10 @@
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
       <c r="F36" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H36" s="13"/>
     </row>
@@ -2092,10 +2147,10 @@
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
       <c r="F37" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H37" s="13"/>
     </row>
@@ -2106,78 +2161,80 @@
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
       <c r="F38" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H38" s="13"/>
     </row>
     <row r="39">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="14"/>
+        <v>106</v>
+      </c>
+      <c r="H39" s="13"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B40" s="8" t="s">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="G40" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="H41" s="14"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D42" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="12"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="H41" s="13"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
+      <c r="E42" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="F42" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="H42" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H42" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="13"/>
@@ -2186,10 +2243,10 @@
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
       <c r="F43" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H43" s="13"/>
     </row>
@@ -2200,10 +2257,10 @@
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H44" s="13"/>
     </row>
@@ -2214,10 +2271,10 @@
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H45" s="13"/>
     </row>
@@ -2228,10 +2285,10 @@
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H46" s="13"/>
     </row>
@@ -2242,10 +2299,10 @@
       <c r="D47" s="13"/>
       <c r="E47" s="13"/>
       <c r="F47" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H47" s="13"/>
     </row>
@@ -2256,10 +2313,10 @@
       <c r="D48" s="13"/>
       <c r="E48" s="13"/>
       <c r="F48" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H48" s="13"/>
     </row>
@@ -2270,182 +2327,188 @@
       <c r="D49" s="13"/>
       <c r="E49" s="13"/>
       <c r="F49" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H49" s="13"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G50" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G49" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H49" s="13"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H50" s="14"/>
+      <c r="H50" s="13"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B51" s="8" t="s">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="G51" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F51" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H51" s="12"/>
+      <c r="H51" s="13"/>
     </row>
     <row r="52">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
       <c r="F52" s="11" t="s">
         <v>115</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="H52" s="13"/>
+      <c r="H52" s="14"/>
     </row>
     <row r="53">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
+      <c r="A53" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="F53" s="11" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H53" s="14"/>
+        <v>92</v>
+      </c>
+      <c r="H53" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H54" s="13"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H55" s="14"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="F56" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H56" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="G57" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H57" s="13"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H58" s="14"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D59" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="H55" s="13"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="H56" s="14"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H57" s="12"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H58" s="13"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
+      <c r="E59" s="8" t="s">
+        <v>131</v>
+      </c>
       <c r="F59" s="11" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H59" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H59" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="13"/>
@@ -2453,79 +2516,81 @@
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
-      <c r="F60" s="22" t="s">
-        <v>130</v>
+      <c r="F60" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="H60" s="13"/>
     </row>
     <row r="61">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
+      <c r="A61" s="13"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
       <c r="F61" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H61" s="13"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H62" s="13"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H63" s="14"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="G61" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="H61" s="14"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G62" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H62" s="12"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="13"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H63" s="13"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="13"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
       <c r="F64" s="11" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H64" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H64" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="13"/>
@@ -2533,11 +2598,11 @@
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
       <c r="E65" s="13"/>
-      <c r="F65" s="22" t="s">
-        <v>135</v>
+      <c r="F65" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H65" s="13"/>
     </row>
@@ -2547,11 +2612,11 @@
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
       <c r="E66" s="13"/>
-      <c r="F66" s="23" t="s">
-        <v>137</v>
+      <c r="F66" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H66" s="13"/>
     </row>
@@ -2561,11 +2626,11 @@
       <c r="C67" s="13"/>
       <c r="D67" s="13"/>
       <c r="E67" s="13"/>
-      <c r="F67" s="22" t="s">
-        <v>139</v>
+      <c r="F67" s="23" t="s">
+        <v>141</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H67" s="13"/>
     </row>
@@ -2575,79 +2640,81 @@
       <c r="C68" s="13"/>
       <c r="D68" s="13"/>
       <c r="E68" s="13"/>
-      <c r="F68" s="23" t="s">
-        <v>141</v>
+      <c r="F68" s="24" t="s">
+        <v>143</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H68" s="13"/>
     </row>
     <row r="69">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="11" t="s">
-        <v>143</v>
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="23" t="s">
+        <v>145</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H69" s="14"/>
+        <v>146</v>
+      </c>
+      <c r="H69" s="13"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" s="9" t="s">
+      <c r="A70" s="13"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H70" s="13"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H71" s="14"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D72" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E70" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H70" s="12"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H71" s="13"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
+      <c r="E72" s="8" t="s">
+        <v>131</v>
+      </c>
       <c r="F72" s="11" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H72" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H72" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="13"/>
@@ -2655,11 +2722,11 @@
       <c r="C73" s="13"/>
       <c r="D73" s="13"/>
       <c r="E73" s="13"/>
-      <c r="F73" s="22" t="s">
-        <v>147</v>
+      <c r="F73" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="H73" s="13"/>
     </row>
@@ -2669,11 +2736,11 @@
       <c r="C74" s="13"/>
       <c r="D74" s="13"/>
       <c r="E74" s="13"/>
-      <c r="F74" s="23" t="s">
-        <v>137</v>
+      <c r="F74" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H74" s="13"/>
     </row>
@@ -2683,11 +2750,11 @@
       <c r="C75" s="13"/>
       <c r="D75" s="13"/>
       <c r="E75" s="13"/>
-      <c r="F75" s="22" t="s">
-        <v>149</v>
+      <c r="F75" s="23" t="s">
+        <v>153</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H75" s="13"/>
     </row>
@@ -2697,145 +2764,149 @@
       <c r="C76" s="13"/>
       <c r="D76" s="13"/>
       <c r="E76" s="13"/>
-      <c r="F76" s="23" t="s">
-        <v>141</v>
+      <c r="F76" s="24" t="s">
+        <v>143</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H76" s="13"/>
     </row>
     <row r="77">
-      <c r="A77" s="14"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="11" t="s">
-        <v>143</v>
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="23" t="s">
+        <v>155</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="H77" s="14"/>
+        <v>156</v>
+      </c>
+      <c r="H77" s="13"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C78" s="9" t="s">
+      <c r="A78" s="13"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H78" s="13"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="H79" s="14"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D80" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E78" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F78" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H78" s="12"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G79" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H79" s="13"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="13"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
+      <c r="E80" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="F80" s="11" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="H80" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H80" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="14"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
+      <c r="A81" s="13"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
       <c r="F81" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="H81" s="14"/>
+        <v>133</v>
+      </c>
+      <c r="H81" s="13"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C82" s="9" t="s">
+      <c r="A82" s="13"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="H82" s="13"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="H83" s="14"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D84" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E82" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G82" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H82" s="12"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="13"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G83" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H83" s="13"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
+      <c r="E84" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="F84" s="11" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="H84" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H84" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="13"/>
@@ -2843,117 +2914,109 @@
       <c r="C85" s="13"/>
       <c r="D85" s="13"/>
       <c r="E85" s="13"/>
-      <c r="F85" s="22" t="s">
+      <c r="F85" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="H85" s="13"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="13"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G86" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G85" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H85" s="13"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="14"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G86" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="H86" s="14"/>
+      <c r="H86" s="13"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C87" s="9" t="s">
+      <c r="A87" s="13"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H87" s="13"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="H88" s="14"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D89" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E87" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="F87" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G87" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H87" s="12"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="13"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G88" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H88" s="13"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="13"/>
-      <c r="B89" s="13"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
+      <c r="E89" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="F89" s="11" t="s">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="H89" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="H89" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="14"/>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
+      <c r="A90" s="13"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
       <c r="F90" s="11" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="H90" s="14"/>
+        <v>133</v>
+      </c>
+      <c r="H90" s="13"/>
     </row>
     <row r="91">
-      <c r="A91" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E91" s="8" t="s">
+      <c r="A91" s="13"/>
+      <c r="B91" s="13"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F91" s="11" t="s">
-        <v>86</v>
-      </c>
       <c r="G91" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H91" s="12"/>
+        <v>174</v>
+      </c>
+      <c r="H91" s="13"/>
     </row>
     <row r="92">
       <c r="A92" s="14"/>
@@ -2962,19 +3025,19 @@
       <c r="D92" s="14"/>
       <c r="E92" s="14"/>
       <c r="F92" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H92" s="14"/>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="s">
-        <v>176</v>
+      <c r="A93" s="25" t="s">
+        <v>177</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>10</v>
@@ -2983,15 +3046,17 @@
         <v>25</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H93" s="12"/>
+        <v>92</v>
+      </c>
+      <c r="H93" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="14"/>
@@ -3000,36 +3065,38 @@
       <c r="D94" s="14"/>
       <c r="E94" s="14"/>
       <c r="F94" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H94" s="14"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="s">
-        <v>180</v>
+      <c r="A95" s="25" t="s">
+        <v>182</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D95" s="10" t="s">
-        <v>11</v>
+      <c r="D95" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H95" s="12"/>
+        <v>92</v>
+      </c>
+      <c r="H95" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="14"/>
@@ -3038,10 +3105,10 @@
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
       <c r="F96" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H96" s="14"/>
     </row>
@@ -3059,15 +3126,15 @@
         <v>11</v>
       </c>
       <c r="E97" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F97" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="F97" s="11" t="s">
+      <c r="G97" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="G97" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="H97" s="12"/>
+      <c r="H97" s="26"/>
     </row>
     <row r="98">
       <c r="A98" s="14"/>
@@ -3076,36 +3143,36 @@
       <c r="D98" s="14"/>
       <c r="E98" s="14"/>
       <c r="F98" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G98" s="11" t="s">
         <v>191</v>
-      </c>
-      <c r="G98" s="11" t="s">
-        <v>192</v>
       </c>
       <c r="H98" s="14"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>193</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>194</v>
       </c>
       <c r="C99" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D99" s="15" t="s">
-        <v>25</v>
+      <c r="D99" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="E99" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="F99" s="11" t="s">
+      <c r="G99" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="G99" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="H99" s="12"/>
+      <c r="H99" s="26"/>
     </row>
     <row r="100">
       <c r="A100" s="14"/>
@@ -3114,7 +3181,7 @@
       <c r="D100" s="14"/>
       <c r="E100" s="14"/>
       <c r="F100" s="11" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G100" s="11" t="s">
         <v>198</v>
@@ -3131,19 +3198,19 @@
       <c r="C101" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D101" s="10" t="s">
-        <v>11</v>
+      <c r="D101" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>36</v>
+        <v>201</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H101" s="12"/>
+        <v>203</v>
+      </c>
+      <c r="H101" s="26"/>
     </row>
     <row r="102">
       <c r="A102" s="14"/>
@@ -3152,320 +3219,320 @@
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
       <c r="F102" s="11" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H102" s="14"/>
     </row>
     <row r="103">
-      <c r="A103" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B103" s="18" t="s">
+      <c r="A103" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="B103" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D103" s="20" t="s">
+      <c r="D103" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="H103" s="26"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="14"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H104" s="14"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="F103" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="G103" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="H103" s="21"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B104" s="18" t="s">
+      <c r="E105" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="C104" s="19" t="s">
+      <c r="F105" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G105" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="H105" s="27"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B106" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C106" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D104" s="20" t="s">
+      <c r="D106" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E104" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="F104" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="G104" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="H104" s="21"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="8" t="s">
+      <c r="E106" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="F106" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G106" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B105" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C105" s="9" t="s">
+      <c r="H106" s="27"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C107" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D105" s="15" t="s">
+      <c r="D107" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E105" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F105" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G105" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H105" s="12"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="13"/>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G106" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="H106" s="13"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="14"/>
-      <c r="B107" s="14"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
+      <c r="E107" s="8" t="s">
+        <v>210</v>
+      </c>
       <c r="F107" s="11" t="s">
         <v>218</v>
       </c>
       <c r="G107" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="H107" s="14"/>
+      <c r="H107" s="26"/>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="13"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="G108" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="H108" s="13"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="14"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G109" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H109" s="14"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C110" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D108" s="15" t="s">
+      <c r="D110" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E108" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F108" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G108" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H108" s="12"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="13"/>
-      <c r="B109" s="13"/>
-      <c r="C109" s="13"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G109" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="H109" s="13"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="14"/>
-      <c r="B110" s="14"/>
-      <c r="C110" s="14"/>
-      <c r="D110" s="14"/>
-      <c r="E110" s="14"/>
+      <c r="E110" s="8" t="s">
+        <v>210</v>
+      </c>
       <c r="F110" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G110" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="H110" s="14"/>
+      <c r="H110" s="26"/>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="13"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="G111" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="H111" s="13"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="14"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C111" s="9" t="s">
+      <c r="H112" s="14"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C113" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D111" s="15" t="s">
+      <c r="D113" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E111" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G111" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H111" s="12"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="13"/>
-      <c r="B112" s="13"/>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G112" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="H112" s="13"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="13"/>
-      <c r="B113" s="13"/>
-      <c r="C113" s="13"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
+      <c r="E113" s="8" t="s">
+        <v>229</v>
+      </c>
       <c r="F113" s="11" t="s">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="H113" s="13"/>
+        <v>219</v>
+      </c>
+      <c r="H113" s="26"/>
     </row>
     <row r="114">
-      <c r="A114" s="14"/>
-      <c r="B114" s="14"/>
-      <c r="C114" s="14"/>
-      <c r="D114" s="14"/>
-      <c r="E114" s="14"/>
+      <c r="A114" s="13"/>
+      <c r="B114" s="13"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
       <c r="F114" s="11" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="H114" s="14"/>
+        <v>221</v>
+      </c>
+      <c r="H114" s="13"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B115" s="8" t="s">
+      <c r="A115" s="13"/>
+      <c r="B115" s="13"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
+      <c r="F115" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G115" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C115" s="9" t="s">
+      <c r="H115" s="13"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="G116" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="H116" s="14"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C117" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D115" s="15" t="s">
+      <c r="D117" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E115" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="F115" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="G115" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H115" s="12"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="13"/>
-      <c r="B116" s="13"/>
-      <c r="C116" s="13"/>
-      <c r="D116" s="13"/>
-      <c r="E116" s="13"/>
-      <c r="F116" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="G116" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="H116" s="13"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="13"/>
-      <c r="B117" s="13"/>
-      <c r="C117" s="13"/>
-      <c r="D117" s="13"/>
-      <c r="E117" s="13"/>
+      <c r="E117" s="8" t="s">
+        <v>235</v>
+      </c>
       <c r="F117" s="11" t="s">
-        <v>47</v>
+        <v>236</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="H117" s="13"/>
+        <v>219</v>
+      </c>
+      <c r="H117" s="26"/>
     </row>
     <row r="118">
-      <c r="A118" s="14"/>
-      <c r="B118" s="14"/>
-      <c r="C118" s="14"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="14"/>
+      <c r="A118" s="13"/>
+      <c r="B118" s="13"/>
+      <c r="C118" s="13"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="13"/>
       <c r="F118" s="11" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="H118" s="14"/>
+        <v>221</v>
+      </c>
+      <c r="H118" s="13"/>
     </row>
     <row r="119">
-      <c r="A119" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F119" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="G119" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="H119" s="12"/>
+      <c r="A119" s="13"/>
+      <c r="B119" s="13"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G119" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="H119" s="13"/>
     </row>
     <row r="120">
       <c r="A120" s="14"/>
@@ -3473,65 +3540,75 @@
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
-      <c r="F120" s="16" t="s">
+      <c r="F120" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="G120" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="H120" s="14"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="B121" s="8" t="s">
         <v>240</v>
-      </c>
-      <c r="G120" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="H120" s="14"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>243</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D121" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F121" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="G121" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="H121" s="26"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="14"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="14"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="14"/>
+      <c r="F122" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="H122" s="14"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E121" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F121" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="G121" s="11" t="s">
+      <c r="E123" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="G123" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H121" s="12"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="13"/>
-      <c r="B122" s="13"/>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="G122" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H122" s="13"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="13"/>
-      <c r="B123" s="13"/>
-      <c r="C123" s="13"/>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
-      <c r="F123" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="G123" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="H123" s="13"/>
+      <c r="H123" s="26"/>
     </row>
     <row r="124">
       <c r="A124" s="13"/>
@@ -3540,10 +3617,10 @@
       <c r="D124" s="13"/>
       <c r="E124" s="13"/>
       <c r="F124" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G124" s="11" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="H124" s="13"/>
     </row>
@@ -3554,10 +3631,10 @@
       <c r="D125" s="13"/>
       <c r="E125" s="13"/>
       <c r="F125" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H125" s="13"/>
     </row>
@@ -3568,10 +3645,10 @@
       <c r="D126" s="13"/>
       <c r="E126" s="13"/>
       <c r="F126" s="11" t="s">
-        <v>96</v>
+        <v>252</v>
       </c>
       <c r="G126" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H126" s="13"/>
     </row>
@@ -3582,78 +3659,78 @@
       <c r="D127" s="13"/>
       <c r="E127" s="13"/>
       <c r="F127" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="H127" s="13"/>
     </row>
     <row r="128">
-      <c r="A128" s="14"/>
-      <c r="B128" s="14"/>
-      <c r="C128" s="14"/>
-      <c r="D128" s="14"/>
-      <c r="E128" s="14"/>
+      <c r="A128" s="13"/>
+      <c r="B128" s="13"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
       <c r="F128" s="11" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="G128" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="H128" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="H128" s="13"/>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B129" s="8" t="s">
+      <c r="A129" s="13"/>
+      <c r="B129" s="13"/>
+      <c r="C129" s="13"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C129" s="9" t="s">
+      <c r="G129" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H129" s="13"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="14"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="14"/>
+      <c r="D130" s="14"/>
+      <c r="E130" s="14"/>
+      <c r="F130" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G130" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="H130" s="14"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D129" s="15" t="s">
+      <c r="D131" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E129" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F129" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G129" s="11" t="s">
+      <c r="E131" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G131" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H129" s="12"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="13"/>
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
-      <c r="F130" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="G130" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H130" s="13"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="13"/>
-      <c r="B131" s="13"/>
-      <c r="C131" s="13"/>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
-      <c r="F131" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="G131" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="H131" s="13"/>
+      <c r="H131" s="26"/>
     </row>
     <row r="132">
       <c r="A132" s="13"/>
@@ -3662,10 +3739,10 @@
       <c r="D132" s="13"/>
       <c r="E132" s="13"/>
       <c r="F132" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G132" s="11" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="H132" s="13"/>
     </row>
@@ -3676,10 +3753,10 @@
       <c r="D133" s="13"/>
       <c r="E133" s="13"/>
       <c r="F133" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H133" s="13"/>
     </row>
@@ -3690,10 +3767,10 @@
       <c r="D134" s="13"/>
       <c r="E134" s="13"/>
       <c r="F134" s="11" t="s">
-        <v>96</v>
+        <v>252</v>
       </c>
       <c r="G134" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H134" s="13"/>
     </row>
@@ -3704,10 +3781,10 @@
       <c r="D135" s="13"/>
       <c r="E135" s="13"/>
       <c r="F135" s="11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H135" s="13"/>
     </row>
@@ -3718,10 +3795,10 @@
       <c r="D136" s="13"/>
       <c r="E136" s="13"/>
       <c r="F136" s="11" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="G136" s="11" t="s">
-        <v>253</v>
+        <v>102</v>
       </c>
       <c r="H136" s="13"/>
     </row>
@@ -3731,79 +3808,79 @@
       <c r="C137" s="13"/>
       <c r="D137" s="13"/>
       <c r="E137" s="13"/>
-      <c r="F137" s="25">
+      <c r="F137" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="G137" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="H137" s="13"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="13"/>
+      <c r="B138" s="13"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G138" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="H138" s="13"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="13"/>
+      <c r="B139" s="13"/>
+      <c r="C139" s="13"/>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="28">
         <v>9.0</v>
       </c>
-      <c r="G137" s="25">
+      <c r="G139" s="28">
         <v>9.0</v>
       </c>
-      <c r="H137" s="13"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="14"/>
-      <c r="B138" s="14"/>
-      <c r="C138" s="14"/>
-      <c r="D138" s="14"/>
-      <c r="E138" s="14"/>
-      <c r="F138" s="25">
+      <c r="H139" s="13"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="14"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="14"/>
+      <c r="D140" s="14"/>
+      <c r="E140" s="14"/>
+      <c r="F140" s="28">
         <v>10.0</v>
       </c>
-      <c r="G138" s="25">
+      <c r="G140" s="28">
         <v>10.0</v>
       </c>
-      <c r="H138" s="14"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B139" s="8" t="s">
+      <c r="H140" s="14"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F141" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="C139" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D139" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F139" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G139" s="11" t="s">
+      <c r="G141" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H139" s="12"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="13"/>
-      <c r="B140" s="13"/>
-      <c r="C140" s="13"/>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
-      <c r="F140" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="G140" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H140" s="13"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="13"/>
-      <c r="B141" s="13"/>
-      <c r="C141" s="13"/>
-      <c r="D141" s="13"/>
-      <c r="E141" s="13"/>
-      <c r="F141" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="G141" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H141" s="13"/>
+      <c r="H141" s="26"/>
     </row>
     <row r="142">
       <c r="A142" s="13"/>
@@ -3812,10 +3889,10 @@
       <c r="D142" s="13"/>
       <c r="E142" s="13"/>
       <c r="F142" s="11" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="G142" s="11" t="s">
-        <v>263</v>
+        <v>16</v>
       </c>
       <c r="H142" s="13"/>
     </row>
@@ -3826,10 +3903,10 @@
       <c r="D143" s="13"/>
       <c r="E143" s="13"/>
       <c r="F143" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H143" s="13"/>
     </row>
@@ -3840,78 +3917,78 @@
       <c r="D144" s="13"/>
       <c r="E144" s="13"/>
       <c r="F144" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="H144" s="13"/>
     </row>
     <row r="145">
-      <c r="A145" s="14"/>
-      <c r="B145" s="14"/>
-      <c r="C145" s="14"/>
-      <c r="D145" s="14"/>
-      <c r="E145" s="14"/>
+      <c r="A145" s="13"/>
+      <c r="B145" s="13"/>
+      <c r="C145" s="13"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
       <c r="F145" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G145" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="H145" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="H145" s="13"/>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B146" s="8" t="s">
+      <c r="A146" s="13"/>
+      <c r="B146" s="13"/>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
+      <c r="F146" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="G146" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H146" s="13"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="14"/>
+      <c r="B147" s="14"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="14"/>
+      <c r="E147" s="14"/>
+      <c r="F147" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="G147" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="H147" s="14"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C148" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D146" s="15" t="s">
+      <c r="D148" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E146" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F146" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G146" s="11" t="s">
+      <c r="E148" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F148" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G148" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="12"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="13"/>
-      <c r="B147" s="13"/>
-      <c r="C147" s="13"/>
-      <c r="D147" s="13"/>
-      <c r="E147" s="13"/>
-      <c r="F147" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="G147" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H147" s="13"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="13"/>
-      <c r="B148" s="13"/>
-      <c r="C148" s="13"/>
-      <c r="D148" s="13"/>
-      <c r="E148" s="13"/>
-      <c r="F148" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="G148" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="H148" s="13"/>
+      <c r="H148" s="26"/>
     </row>
     <row r="149">
       <c r="A149" s="13"/>
@@ -3920,10 +3997,10 @@
       <c r="D149" s="13"/>
       <c r="E149" s="13"/>
       <c r="F149" s="11" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="G149" s="11" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="H149" s="13"/>
     </row>
@@ -3934,10 +4011,10 @@
       <c r="D150" s="13"/>
       <c r="E150" s="13"/>
       <c r="F150" s="11" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="G150" s="11" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H150" s="13"/>
     </row>
@@ -3948,76 +4025,76 @@
       <c r="D151" s="13"/>
       <c r="E151" s="13"/>
       <c r="F151" s="11" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G151" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H151" s="13"/>
     </row>
     <row r="152">
-      <c r="A152" s="14"/>
-      <c r="B152" s="14"/>
-      <c r="C152" s="14"/>
-      <c r="D152" s="14"/>
-      <c r="E152" s="14"/>
+      <c r="A152" s="13"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
       <c r="F152" s="11" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="H152" s="13"/>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="B153" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C153" s="9" t="s">
+      <c r="A153" s="13"/>
+      <c r="B153" s="13"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="13"/>
+      <c r="F153" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="G153" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H153" s="13"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="14"/>
+      <c r="B154" s="14"/>
+      <c r="C154" s="14"/>
+      <c r="D154" s="14"/>
+      <c r="E154" s="14"/>
+      <c r="F154" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="G154" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="H154" s="13"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C155" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D153" s="15" t="s">
+      <c r="D155" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E153" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F153" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G153" s="11" t="s">
+      <c r="E155" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F155" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G155" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="H153" s="13"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="13"/>
-      <c r="B154" s="13"/>
-      <c r="C154" s="13"/>
-      <c r="D154" s="13"/>
-      <c r="E154" s="13"/>
-      <c r="F154" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="G154" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H154" s="13"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="13"/>
-      <c r="B155" s="13"/>
-      <c r="C155" s="13"/>
-      <c r="D155" s="13"/>
-      <c r="E155" s="13"/>
-      <c r="F155" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="G155" s="11" t="s">
-        <v>247</v>
       </c>
       <c r="H155" s="13"/>
     </row>
@@ -4028,10 +4105,10 @@
       <c r="D156" s="13"/>
       <c r="E156" s="13"/>
       <c r="F156" s="11" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G156" s="11" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="H156" s="13"/>
     </row>
@@ -4042,10 +4119,10 @@
       <c r="D157" s="13"/>
       <c r="E157" s="13"/>
       <c r="F157" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G157" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H157" s="13"/>
     </row>
@@ -4056,10 +4133,10 @@
       <c r="D158" s="13"/>
       <c r="E158" s="13"/>
       <c r="F158" s="11" t="s">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="G158" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H158" s="13"/>
     </row>
@@ -4070,78 +4147,78 @@
       <c r="D159" s="13"/>
       <c r="E159" s="13"/>
       <c r="F159" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G159" s="11" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="H159" s="13"/>
     </row>
     <row r="160">
-      <c r="A160" s="14"/>
-      <c r="B160" s="14"/>
-      <c r="C160" s="14"/>
-      <c r="D160" s="14"/>
-      <c r="E160" s="14"/>
+      <c r="A160" s="13"/>
+      <c r="B160" s="13"/>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
       <c r="F160" s="11" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="G160" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="H160" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="H160" s="13"/>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B161" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C161" s="9" t="s">
+      <c r="A161" s="13"/>
+      <c r="B161" s="13"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="13"/>
+      <c r="F161" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G161" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H161" s="13"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="14"/>
+      <c r="B162" s="14"/>
+      <c r="C162" s="14"/>
+      <c r="D162" s="14"/>
+      <c r="E162" s="14"/>
+      <c r="F162" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G162" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="H162" s="14"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C163" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D161" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F161" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="G161" s="11" t="s">
+      <c r="D163" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="G163" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H161" s="12"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="13"/>
-      <c r="B162" s="13"/>
-      <c r="C162" s="13"/>
-      <c r="D162" s="13"/>
-      <c r="E162" s="13"/>
-      <c r="F162" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="G162" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H162" s="13"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="13"/>
-      <c r="B163" s="13"/>
-      <c r="C163" s="13"/>
-      <c r="D163" s="13"/>
-      <c r="E163" s="13"/>
-      <c r="F163" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="G163" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H163" s="13"/>
+      <c r="H163" s="26"/>
     </row>
     <row r="164">
       <c r="A164" s="13"/>
@@ -4150,10 +4227,10 @@
       <c r="D164" s="13"/>
       <c r="E164" s="13"/>
       <c r="F164" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G164" s="11" t="s">
-        <v>279</v>
+        <v>32</v>
       </c>
       <c r="H164" s="13"/>
     </row>
@@ -4164,78 +4241,78 @@
       <c r="D165" s="13"/>
       <c r="E165" s="13"/>
       <c r="F165" s="11" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="G165" s="11" t="s">
-        <v>272</v>
+        <v>135</v>
       </c>
       <c r="H165" s="13"/>
     </row>
     <row r="166">
-      <c r="A166" s="14"/>
-      <c r="B166" s="14"/>
-      <c r="C166" s="14"/>
-      <c r="D166" s="14"/>
-      <c r="E166" s="14"/>
+      <c r="A166" s="13"/>
+      <c r="B166" s="13"/>
+      <c r="C166" s="13"/>
+      <c r="D166" s="13"/>
+      <c r="E166" s="13"/>
       <c r="F166" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G166" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="H166" s="14"/>
+        <v>283</v>
+      </c>
+      <c r="H166" s="13"/>
     </row>
     <row r="167">
-      <c r="A167" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="B167" s="8" t="s">
+      <c r="A167" s="13"/>
+      <c r="B167" s="13"/>
+      <c r="C167" s="13"/>
+      <c r="D167" s="13"/>
+      <c r="E167" s="13"/>
+      <c r="F167" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="C167" s="9" t="s">
+      <c r="G167" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H167" s="13"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="14"/>
+      <c r="B168" s="14"/>
+      <c r="C168" s="14"/>
+      <c r="D168" s="14"/>
+      <c r="E168" s="14"/>
+      <c r="F168" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="G168" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="H168" s="14"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C169" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D167" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F167" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G167" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="H167" s="12"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="13"/>
-      <c r="B168" s="13"/>
-      <c r="C168" s="13"/>
-      <c r="D168" s="13"/>
-      <c r="E168" s="13"/>
-      <c r="F168" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="G168" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H168" s="13"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="13"/>
-      <c r="B169" s="13"/>
-      <c r="C169" s="13"/>
-      <c r="D169" s="13"/>
-      <c r="E169" s="13"/>
+      <c r="D169" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>241</v>
+      </c>
       <c r="F169" s="11" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="G169" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="H169" s="13"/>
+        <v>289</v>
+      </c>
+      <c r="H169" s="26"/>
     </row>
     <row r="170">
       <c r="A170" s="13"/>
@@ -4244,10 +4321,10 @@
       <c r="D170" s="13"/>
       <c r="E170" s="13"/>
       <c r="F170" s="11" t="s">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="G170" s="11" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="H170" s="13"/>
     </row>
@@ -4258,10 +4335,10 @@
       <c r="D171" s="13"/>
       <c r="E171" s="13"/>
       <c r="F171" s="11" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="G171" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H171" s="13"/>
     </row>
@@ -4272,10 +4349,10 @@
       <c r="D172" s="13"/>
       <c r="E172" s="13"/>
       <c r="F172" s="11" t="s">
-        <v>96</v>
+        <v>252</v>
       </c>
       <c r="G172" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H172" s="13"/>
     </row>
@@ -4286,78 +4363,78 @@
       <c r="D173" s="13"/>
       <c r="E173" s="13"/>
       <c r="F173" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G173" s="11" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="H173" s="13"/>
     </row>
     <row r="174">
-      <c r="A174" s="14"/>
-      <c r="B174" s="14"/>
-      <c r="C174" s="14"/>
-      <c r="D174" s="14"/>
-      <c r="E174" s="14"/>
+      <c r="A174" s="13"/>
+      <c r="B174" s="13"/>
+      <c r="C174" s="13"/>
+      <c r="D174" s="13"/>
+      <c r="E174" s="13"/>
       <c r="F174" s="11" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="G174" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="H174" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="H174" s="13"/>
     </row>
     <row r="175">
-      <c r="A175" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="C175" s="9" t="s">
+      <c r="A175" s="13"/>
+      <c r="B175" s="13"/>
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="13"/>
+      <c r="F175" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G175" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H175" s="13"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="14"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="14"/>
+      <c r="D176" s="14"/>
+      <c r="E176" s="14"/>
+      <c r="F176" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G176" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="H176" s="14"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C177" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D175" s="10" t="s">
+      <c r="D177" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E175" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F175" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G175" s="11" t="s">
+      <c r="E177" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F177" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G177" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H175" s="12"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="13"/>
-      <c r="B176" s="13"/>
-      <c r="C176" s="13"/>
-      <c r="D176" s="13"/>
-      <c r="E176" s="13"/>
-      <c r="F176" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="G176" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H176" s="13"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="13"/>
-      <c r="B177" s="13"/>
-      <c r="C177" s="13"/>
-      <c r="D177" s="13"/>
-      <c r="E177" s="13"/>
-      <c r="F177" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="G177" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="H177" s="13"/>
+      <c r="H177" s="26"/>
     </row>
     <row r="178">
       <c r="A178" s="13"/>
@@ -4366,10 +4443,10 @@
       <c r="D178" s="13"/>
       <c r="E178" s="13"/>
       <c r="F178" s="11" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="G178" s="11" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="H178" s="13"/>
     </row>
@@ -4380,10 +4457,10 @@
       <c r="D179" s="13"/>
       <c r="E179" s="13"/>
       <c r="F179" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G179" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H179" s="13"/>
     </row>
@@ -4394,10 +4471,10 @@
       <c r="D180" s="13"/>
       <c r="E180" s="13"/>
       <c r="F180" s="11" t="s">
-        <v>96</v>
+        <v>252</v>
       </c>
       <c r="G180" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H180" s="13"/>
     </row>
@@ -4408,287 +4485,321 @@
       <c r="D181" s="13"/>
       <c r="E181" s="13"/>
       <c r="F181" s="11" t="s">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="G181" s="11" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="H181" s="13"/>
     </row>
     <row r="182">
-      <c r="A182" s="14"/>
-      <c r="B182" s="14"/>
-      <c r="C182" s="14"/>
-      <c r="D182" s="14"/>
-      <c r="E182" s="14"/>
+      <c r="A182" s="13"/>
+      <c r="B182" s="13"/>
+      <c r="C182" s="13"/>
+      <c r="D182" s="13"/>
+      <c r="E182" s="13"/>
       <c r="F182" s="11" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="G182" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="H182" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="H182" s="13"/>
     </row>
     <row r="183">
-      <c r="A183" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="B183" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="C183" s="26" t="s">
+      <c r="A183" s="13"/>
+      <c r="B183" s="13"/>
+      <c r="C183" s="13"/>
+      <c r="D183" s="13"/>
+      <c r="E183" s="13"/>
+      <c r="F183" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="G183" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H183" s="13"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="14"/>
+      <c r="B184" s="14"/>
+      <c r="C184" s="14"/>
+      <c r="D184" s="14"/>
+      <c r="E184" s="14"/>
+      <c r="F184" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G184" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="H184" s="14"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="B185" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="C185" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D183" s="20" t="s">
+      <c r="D185" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E183" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="F183" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="G183" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="H183" s="21"/>
+      <c r="E185" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="F185" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="G185" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="H185" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="221">
-    <mergeCell ref="C121:C128"/>
-    <mergeCell ref="A121:A128"/>
-    <mergeCell ref="B121:B128"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="B129:B138"/>
-    <mergeCell ref="C129:C138"/>
-    <mergeCell ref="A129:A138"/>
-    <mergeCell ref="B139:B145"/>
-    <mergeCell ref="C139:C145"/>
-    <mergeCell ref="A139:A145"/>
-    <mergeCell ref="D146:D152"/>
-    <mergeCell ref="D153:D160"/>
-    <mergeCell ref="D167:D174"/>
-    <mergeCell ref="E167:E174"/>
-    <mergeCell ref="D175:D182"/>
-    <mergeCell ref="E175:E182"/>
-    <mergeCell ref="H161:H166"/>
-    <mergeCell ref="C161:C166"/>
-    <mergeCell ref="A167:A174"/>
-    <mergeCell ref="H167:H174"/>
-    <mergeCell ref="B167:B174"/>
-    <mergeCell ref="C167:C174"/>
-    <mergeCell ref="H111:H114"/>
-    <mergeCell ref="H115:H118"/>
-    <mergeCell ref="D121:D128"/>
-    <mergeCell ref="E121:E128"/>
-    <mergeCell ref="H121:H128"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="H129:H138"/>
-    <mergeCell ref="H105:H107"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="H139:H145"/>
-    <mergeCell ref="H146:H160"/>
-    <mergeCell ref="H175:H182"/>
-    <mergeCell ref="B146:B152"/>
-    <mergeCell ref="C146:C152"/>
-    <mergeCell ref="A146:A152"/>
-    <mergeCell ref="B175:B182"/>
-    <mergeCell ref="C175:C182"/>
-    <mergeCell ref="A175:A182"/>
-    <mergeCell ref="D139:D145"/>
-    <mergeCell ref="E139:E145"/>
-    <mergeCell ref="E146:E152"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="D111:D114"/>
-    <mergeCell ref="E111:E114"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B111:B114"/>
-    <mergeCell ref="C111:C114"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="D115:D118"/>
-    <mergeCell ref="E115:E118"/>
-    <mergeCell ref="B115:B118"/>
-    <mergeCell ref="C115:C118"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="E153:E160"/>
-    <mergeCell ref="E161:E166"/>
-    <mergeCell ref="E129:E138"/>
-    <mergeCell ref="B161:B166"/>
-    <mergeCell ref="A161:A166"/>
-    <mergeCell ref="D129:D138"/>
-    <mergeCell ref="B153:B160"/>
-    <mergeCell ref="C153:C160"/>
-    <mergeCell ref="A153:A160"/>
-    <mergeCell ref="D161:D166"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="A30:A39"/>
-    <mergeCell ref="B30:B39"/>
-    <mergeCell ref="C30:C39"/>
-    <mergeCell ref="D30:D39"/>
-    <mergeCell ref="E30:E39"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="H30:H39"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="H5:H7"/>
+  <mergeCells count="227">
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="B59:B63"/>
+    <mergeCell ref="C59:C63"/>
+    <mergeCell ref="D59:D63"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="H59:H63"/>
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="A64:A71"/>
+    <mergeCell ref="B64:B71"/>
+    <mergeCell ref="C64:C71"/>
+    <mergeCell ref="D64:D71"/>
+    <mergeCell ref="E64:E71"/>
+    <mergeCell ref="H64:H71"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="E117:E120"/>
+    <mergeCell ref="A113:A116"/>
+    <mergeCell ref="B113:B116"/>
+    <mergeCell ref="C113:C116"/>
+    <mergeCell ref="D113:D116"/>
+    <mergeCell ref="E113:E116"/>
+    <mergeCell ref="H113:H116"/>
+    <mergeCell ref="A117:A120"/>
+    <mergeCell ref="H117:H120"/>
+    <mergeCell ref="B117:B120"/>
+    <mergeCell ref="C117:C120"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="A123:A130"/>
+    <mergeCell ref="B123:B130"/>
+    <mergeCell ref="C123:C130"/>
+    <mergeCell ref="D123:D130"/>
+    <mergeCell ref="E123:E130"/>
+    <mergeCell ref="H123:H130"/>
+    <mergeCell ref="D141:D147"/>
+    <mergeCell ref="E141:E147"/>
+    <mergeCell ref="A131:A140"/>
+    <mergeCell ref="B131:B140"/>
+    <mergeCell ref="C131:C140"/>
+    <mergeCell ref="D131:D140"/>
+    <mergeCell ref="E131:E140"/>
+    <mergeCell ref="H131:H140"/>
+    <mergeCell ref="A141:A147"/>
+    <mergeCell ref="H141:H147"/>
+    <mergeCell ref="B155:B162"/>
+    <mergeCell ref="C155:C162"/>
+    <mergeCell ref="D155:D162"/>
+    <mergeCell ref="E155:E162"/>
+    <mergeCell ref="B141:B147"/>
+    <mergeCell ref="C141:C147"/>
+    <mergeCell ref="B148:B154"/>
+    <mergeCell ref="C148:C154"/>
+    <mergeCell ref="D148:D154"/>
+    <mergeCell ref="E148:E154"/>
+    <mergeCell ref="H148:H162"/>
+    <mergeCell ref="A148:A154"/>
+    <mergeCell ref="A155:A162"/>
+    <mergeCell ref="B163:B168"/>
+    <mergeCell ref="C163:C168"/>
+    <mergeCell ref="D163:D168"/>
+    <mergeCell ref="E163:E168"/>
+    <mergeCell ref="H163:H168"/>
+    <mergeCell ref="A163:A168"/>
+    <mergeCell ref="A169:A176"/>
+    <mergeCell ref="B169:B176"/>
+    <mergeCell ref="C169:C176"/>
+    <mergeCell ref="D169:D176"/>
+    <mergeCell ref="E169:E176"/>
+    <mergeCell ref="H169:H176"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="H24:H28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="B32:B41"/>
+    <mergeCell ref="C32:C41"/>
+    <mergeCell ref="D32:D41"/>
+    <mergeCell ref="E32:E41"/>
+    <mergeCell ref="H32:H41"/>
+    <mergeCell ref="A32:A41"/>
+    <mergeCell ref="A42:A52"/>
+    <mergeCell ref="B42:B52"/>
+    <mergeCell ref="C42:C52"/>
+    <mergeCell ref="D42:D52"/>
+    <mergeCell ref="E42:E52"/>
+    <mergeCell ref="H42:H52"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="E56:E58"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="A177:A184"/>
+    <mergeCell ref="B177:B184"/>
+    <mergeCell ref="C177:C184"/>
+    <mergeCell ref="D177:D184"/>
+    <mergeCell ref="E177:E184"/>
+    <mergeCell ref="H177:H184"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
     <mergeCell ref="H8:H10"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="H40:H50"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="A40:A50"/>
-    <mergeCell ref="B40:B50"/>
-    <mergeCell ref="C40:C50"/>
-    <mergeCell ref="D40:D50"/>
-    <mergeCell ref="E40:E50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="C11:C13"/>
     <mergeCell ref="D11:D13"/>
     <mergeCell ref="E11:E13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="E16:E19"/>
-    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="C57:C61"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="E80:E83"/>
+    <mergeCell ref="A72:A79"/>
+    <mergeCell ref="B72:B79"/>
+    <mergeCell ref="C72:C79"/>
+    <mergeCell ref="D72:D79"/>
+    <mergeCell ref="E72:E79"/>
+    <mergeCell ref="H72:H79"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="H80:H83"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="C84:C88"/>
+    <mergeCell ref="D84:D88"/>
+    <mergeCell ref="E84:E88"/>
+    <mergeCell ref="H84:H88"/>
+    <mergeCell ref="A84:A88"/>
+    <mergeCell ref="A89:A92"/>
+    <mergeCell ref="B89:B92"/>
+    <mergeCell ref="C89:C92"/>
+    <mergeCell ref="D89:D92"/>
+    <mergeCell ref="E89:E92"/>
+    <mergeCell ref="H89:H92"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="A93:A94"/>
     <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="D93:D94"/>
     <mergeCell ref="E93:E94"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
     <mergeCell ref="D97:D98"/>
     <mergeCell ref="E97:E98"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="H97:H98"/>
     <mergeCell ref="A97:A98"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="C70:C77"/>
-    <mergeCell ref="D70:D77"/>
-    <mergeCell ref="E70:E77"/>
-    <mergeCell ref="B70:B77"/>
-    <mergeCell ref="A70:A77"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="D93:D94"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
     <mergeCell ref="A99:A100"/>
     <mergeCell ref="B99:B100"/>
     <mergeCell ref="C99:C100"/>
     <mergeCell ref="D99:D100"/>
     <mergeCell ref="E99:E100"/>
-    <mergeCell ref="E87:E90"/>
-    <mergeCell ref="D87:D90"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="C87:C90"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="E82:E86"/>
-    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="E103:E104"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="C101:C102"/>
     <mergeCell ref="D101:D102"/>
     <mergeCell ref="E101:E102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="D105:D107"/>
-    <mergeCell ref="E105:E107"/>
-    <mergeCell ref="A105:A107"/>
-    <mergeCell ref="C105:C107"/>
-    <mergeCell ref="B105:B107"/>
-    <mergeCell ref="H87:H90"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
     <mergeCell ref="H101:H102"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="D54:D56"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="B62:B69"/>
-    <mergeCell ref="A62:A69"/>
-    <mergeCell ref="C62:C69"/>
-    <mergeCell ref="E62:E69"/>
-    <mergeCell ref="D62:D69"/>
-    <mergeCell ref="D57:D61"/>
-    <mergeCell ref="E57:E61"/>
-    <mergeCell ref="H57:H61"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="H82:H86"/>
-    <mergeCell ref="H62:H69"/>
-    <mergeCell ref="H70:H77"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="E107:E109"/>
+    <mergeCell ref="H107:H109"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="D110:D112"/>
+    <mergeCell ref="E110:E112"/>
+    <mergeCell ref="H110:H112"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D2 D5 D8 D11 D14 D16 D20:D22 D27 D30 D40 D51 D54 D57 D62 D70 D78 D82 D87 D91 D93 D95 D97 D99 D101 D103:D105 D108 D111 D115 D119 D121 D129 D139 D146 D153 D161 D167 D175 D183">
+    <dataValidation type="list" allowBlank="1" sqref="D2 D5 D8 D11 D14 D16 D18 D22:D24 D29 D32 D42 D53 D56 D59 D64 D72 D80 D84 D89 D93 D95 D97 D99 D101 D103 D105:D107 D110 D113 D117 D121 D123 D131 D141 D148 D155 D163 D169 D177 D185">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F60"/>
-    <hyperlink r:id="rId2" ref="F65"/>
-    <hyperlink r:id="rId3" ref="F67"/>
-    <hyperlink r:id="rId4" ref="F73"/>
-    <hyperlink r:id="rId5" ref="F75"/>
-    <hyperlink r:id="rId6" ref="F85"/>
+    <hyperlink r:id="rId1" ref="F62"/>
+    <hyperlink r:id="rId2" ref="F67"/>
+    <hyperlink r:id="rId3" ref="F69"/>
+    <hyperlink r:id="rId4" ref="F75"/>
+    <hyperlink r:id="rId5" ref="F77"/>
+    <hyperlink r:id="rId6" ref="F87"/>
   </hyperlinks>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="302">
   <si>
     <t>ID</t>
   </si>
@@ -394,9 +394,6 @@
   </si>
   <si>
     <t>Нажатие кнопки "Cancel" при удалении новости</t>
-  </si>
-  <si>
-    <t>2. Появляется сообщение "Are you sure you want to permanently delete the document? These changes cannot be reversed in the future? "</t>
   </si>
   <si>
     <t>3. Нажать "Cancel"</t>
@@ -2466,7 +2463,7 @@
         <v>120</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H57" s="13"/>
     </row>
@@ -2477,19 +2474,19 @@
       <c r="D58" s="14"/>
       <c r="E58" s="14"/>
       <c r="F58" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>128</v>
       </c>
       <c r="H58" s="14"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>130</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>10</v>
@@ -2498,7 +2495,7 @@
         <v>25</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>91</v>
@@ -2517,10 +2514,10 @@
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
       <c r="F60" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G60" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="G60" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="H60" s="13"/>
     </row>
@@ -2531,10 +2528,10 @@
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
       <c r="F61" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G61" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="H61" s="13"/>
     </row>
@@ -2545,7 +2542,7 @@
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
       <c r="F62" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>98</v>
@@ -2559,19 +2556,19 @@
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G63" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>138</v>
       </c>
       <c r="H63" s="14"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>139</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>140</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>10</v>
@@ -2580,7 +2577,7 @@
         <v>25</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>91</v>
@@ -2599,10 +2596,10 @@
       <c r="D65" s="13"/>
       <c r="E65" s="13"/>
       <c r="F65" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G65" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="G65" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="H65" s="13"/>
     </row>
@@ -2613,10 +2610,10 @@
       <c r="D66" s="13"/>
       <c r="E66" s="13"/>
       <c r="F66" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G66" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="G66" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="H66" s="13"/>
     </row>
@@ -2627,10 +2624,10 @@
       <c r="D67" s="13"/>
       <c r="E67" s="13"/>
       <c r="F67" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="G67" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="H67" s="13"/>
     </row>
@@ -2641,10 +2638,10 @@
       <c r="D68" s="13"/>
       <c r="E68" s="13"/>
       <c r="F68" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="G68" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="G68" s="11" t="s">
-        <v>144</v>
       </c>
       <c r="H68" s="13"/>
     </row>
@@ -2655,10 +2652,10 @@
       <c r="D69" s="13"/>
       <c r="E69" s="13"/>
       <c r="F69" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G69" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="H69" s="13"/>
     </row>
@@ -2669,10 +2666,10 @@
       <c r="D70" s="13"/>
       <c r="E70" s="13"/>
       <c r="F70" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="G70" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>148</v>
       </c>
       <c r="H70" s="13"/>
     </row>
@@ -2683,19 +2680,19 @@
       <c r="D71" s="14"/>
       <c r="E71" s="14"/>
       <c r="F71" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G71" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="H71" s="14"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>10</v>
@@ -2704,7 +2701,7 @@
         <v>25</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>91</v>
@@ -2723,10 +2720,10 @@
       <c r="D73" s="13"/>
       <c r="E73" s="13"/>
       <c r="F73" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G73" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="H73" s="13"/>
     </row>
@@ -2737,10 +2734,10 @@
       <c r="D74" s="13"/>
       <c r="E74" s="13"/>
       <c r="F74" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G74" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="G74" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="H74" s="13"/>
     </row>
@@ -2751,10 +2748,10 @@
       <c r="D75" s="13"/>
       <c r="E75" s="13"/>
       <c r="F75" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G75" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="G75" s="11" t="s">
-        <v>154</v>
       </c>
       <c r="H75" s="13"/>
     </row>
@@ -2765,10 +2762,10 @@
       <c r="D76" s="13"/>
       <c r="E76" s="13"/>
       <c r="F76" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="G76" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="G76" s="11" t="s">
-        <v>144</v>
       </c>
       <c r="H76" s="13"/>
     </row>
@@ -2779,10 +2776,10 @@
       <c r="D77" s="13"/>
       <c r="E77" s="13"/>
       <c r="F77" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="G77" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="G77" s="11" t="s">
-        <v>156</v>
       </c>
       <c r="H77" s="13"/>
     </row>
@@ -2793,10 +2790,10 @@
       <c r="D78" s="13"/>
       <c r="E78" s="13"/>
       <c r="F78" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="G78" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>148</v>
       </c>
       <c r="H78" s="13"/>
     </row>
@@ -2807,19 +2804,19 @@
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
       <c r="F79" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H79" s="14"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>159</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>10</v>
@@ -2828,7 +2825,7 @@
         <v>25</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>91</v>
@@ -2847,10 +2844,10 @@
       <c r="D81" s="13"/>
       <c r="E81" s="13"/>
       <c r="F81" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G81" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="G81" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="H81" s="13"/>
     </row>
@@ -2861,10 +2858,10 @@
       <c r="D82" s="13"/>
       <c r="E82" s="13"/>
       <c r="F82" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G82" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="G82" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="H82" s="13"/>
     </row>
@@ -2875,19 +2872,19 @@
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H83" s="14"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B84" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>165</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>10</v>
@@ -2896,7 +2893,7 @@
         <v>25</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>91</v>
@@ -2915,10 +2912,10 @@
       <c r="D85" s="13"/>
       <c r="E85" s="13"/>
       <c r="F85" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G85" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="G85" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="H85" s="13"/>
     </row>
@@ -2929,10 +2926,10 @@
       <c r="D86" s="13"/>
       <c r="E86" s="13"/>
       <c r="F86" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H86" s="13"/>
     </row>
@@ -2943,7 +2940,7 @@
       <c r="D87" s="13"/>
       <c r="E87" s="13"/>
       <c r="F87" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G87" s="11" t="s">
         <v>98</v>
@@ -2957,19 +2954,19 @@
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H88" s="14"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B89" s="8" t="s">
         <v>170</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>171</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>10</v>
@@ -2978,7 +2975,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>91</v>
@@ -2997,10 +2994,10 @@
       <c r="D90" s="13"/>
       <c r="E90" s="13"/>
       <c r="F90" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G90" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="G90" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="H90" s="13"/>
     </row>
@@ -3011,10 +3008,10 @@
       <c r="D91" s="13"/>
       <c r="E91" s="13"/>
       <c r="F91" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G91" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="H91" s="13"/>
     </row>
@@ -3025,19 +3022,19 @@
       <c r="D92" s="14"/>
       <c r="E92" s="14"/>
       <c r="F92" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G92" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="H92" s="14"/>
     </row>
     <row r="93">
       <c r="A93" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>178</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>10</v>
@@ -3046,7 +3043,7 @@
         <v>25</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>91</v>
@@ -3065,19 +3062,19 @@
       <c r="D94" s="14"/>
       <c r="E94" s="14"/>
       <c r="F94" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="G94" s="11" t="s">
         <v>180</v>
-      </c>
-      <c r="G94" s="11" t="s">
-        <v>181</v>
       </c>
       <c r="H94" s="14"/>
     </row>
     <row r="95">
       <c r="A95" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="B95" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>183</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>10</v>
@@ -3086,7 +3083,7 @@
         <v>25</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>91</v>
@@ -3105,19 +3102,19 @@
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
       <c r="F96" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H96" s="14"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B97" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="C97" s="9" t="s">
         <v>10</v>
@@ -3129,10 +3126,10 @@
         <v>63</v>
       </c>
       <c r="F97" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G97" s="11" t="s">
         <v>188</v>
-      </c>
-      <c r="G97" s="11" t="s">
-        <v>189</v>
       </c>
       <c r="H97" s="26"/>
     </row>
@@ -3143,19 +3140,19 @@
       <c r="D98" s="14"/>
       <c r="E98" s="14"/>
       <c r="F98" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G98" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="G98" s="11" t="s">
-        <v>191</v>
       </c>
       <c r="H98" s="14"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>193</v>
       </c>
       <c r="C99" s="9" t="s">
         <v>10</v>
@@ -3164,13 +3161,13 @@
         <v>11</v>
       </c>
       <c r="E99" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="F99" s="11" t="s">
+      <c r="G99" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="G99" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="H99" s="26"/>
     </row>
@@ -3181,19 +3178,19 @@
       <c r="D100" s="14"/>
       <c r="E100" s="14"/>
       <c r="F100" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G100" s="11" t="s">
         <v>197</v>
-      </c>
-      <c r="G100" s="11" t="s">
-        <v>198</v>
       </c>
       <c r="H100" s="14"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>200</v>
       </c>
       <c r="C101" s="9" t="s">
         <v>10</v>
@@ -3202,13 +3199,13 @@
         <v>25</v>
       </c>
       <c r="E101" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F101" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F101" s="11" t="s">
+      <c r="G101" s="11" t="s">
         <v>202</v>
-      </c>
-      <c r="G101" s="11" t="s">
-        <v>203</v>
       </c>
       <c r="H101" s="26"/>
     </row>
@@ -3219,19 +3216,19 @@
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
       <c r="F102" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H102" s="14"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" s="8" t="s">
         <v>205</v>
-      </c>
-      <c r="B103" s="8" t="s">
-        <v>206</v>
       </c>
       <c r="C103" s="9" t="s">
         <v>10</v>
@@ -3246,7 +3243,7 @@
         <v>43</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H103" s="26"/>
     </row>
@@ -3266,10 +3263,10 @@
     </row>
     <row r="105">
       <c r="A105" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" s="18" t="s">
         <v>208</v>
-      </c>
-      <c r="B105" s="18" t="s">
-        <v>209</v>
       </c>
       <c r="C105" s="19" t="s">
         <v>10</v>
@@ -3278,22 +3275,22 @@
         <v>25</v>
       </c>
       <c r="E105" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F105" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="F105" s="11" t="s">
+      <c r="G105" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="G105" s="11" t="s">
-        <v>212</v>
       </c>
       <c r="H105" s="27"/>
     </row>
     <row r="106">
       <c r="A106" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="18" t="s">
         <v>213</v>
-      </c>
-      <c r="B106" s="18" t="s">
-        <v>214</v>
       </c>
       <c r="C106" s="19" t="s">
         <v>10</v>
@@ -3302,22 +3299,22 @@
         <v>25</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H106" s="27"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B107" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="B107" s="8" t="s">
-        <v>217</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>10</v>
@@ -3326,13 +3323,13 @@
         <v>25</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F107" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G107" s="11" t="s">
         <v>218</v>
-      </c>
-      <c r="G107" s="11" t="s">
-        <v>219</v>
       </c>
       <c r="H107" s="26"/>
     </row>
@@ -3343,10 +3340,10 @@
       <c r="D108" s="13"/>
       <c r="E108" s="13"/>
       <c r="F108" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G108" s="11" t="s">
         <v>220</v>
-      </c>
-      <c r="G108" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="H108" s="13"/>
     </row>
@@ -3357,19 +3354,19 @@
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
       <c r="F109" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G109" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="G109" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="H109" s="14"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B110" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>225</v>
       </c>
       <c r="C110" s="9" t="s">
         <v>10</v>
@@ -3378,13 +3375,13 @@
         <v>25</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F110" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G110" s="11" t="s">
         <v>218</v>
-      </c>
-      <c r="G110" s="11" t="s">
-        <v>219</v>
       </c>
       <c r="H110" s="26"/>
     </row>
@@ -3395,10 +3392,10 @@
       <c r="D111" s="13"/>
       <c r="E111" s="13"/>
       <c r="F111" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G111" s="11" t="s">
         <v>220</v>
-      </c>
-      <c r="G111" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="H111" s="13"/>
     </row>
@@ -3409,19 +3406,19 @@
       <c r="D112" s="14"/>
       <c r="E112" s="14"/>
       <c r="F112" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H112" s="14"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="B113" s="8" t="s">
-        <v>228</v>
       </c>
       <c r="C113" s="9" t="s">
         <v>10</v>
@@ -3430,13 +3427,13 @@
         <v>25</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F113" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G113" s="11" t="s">
         <v>218</v>
-      </c>
-      <c r="G113" s="11" t="s">
-        <v>219</v>
       </c>
       <c r="H113" s="26"/>
     </row>
@@ -3447,10 +3444,10 @@
       <c r="D114" s="13"/>
       <c r="E114" s="13"/>
       <c r="F114" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G114" s="11" t="s">
         <v>220</v>
-      </c>
-      <c r="G114" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="H114" s="13"/>
     </row>
@@ -3464,7 +3461,7 @@
         <v>51</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H115" s="13"/>
     </row>
@@ -3475,19 +3472,19 @@
       <c r="D116" s="14"/>
       <c r="E116" s="14"/>
       <c r="F116" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G116" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="G116" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="H116" s="14"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>234</v>
       </c>
       <c r="C117" s="9" t="s">
         <v>10</v>
@@ -3496,13 +3493,13 @@
         <v>25</v>
       </c>
       <c r="E117" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="F117" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F117" s="11" t="s">
-        <v>236</v>
-      </c>
       <c r="G117" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H117" s="26"/>
     </row>
@@ -3513,10 +3510,10 @@
       <c r="D118" s="13"/>
       <c r="E118" s="13"/>
       <c r="F118" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H118" s="13"/>
     </row>
@@ -3530,7 +3527,7 @@
         <v>51</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H119" s="13"/>
     </row>
@@ -3541,19 +3538,19 @@
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
       <c r="F120" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H120" s="14"/>
     </row>
     <row r="121">
       <c r="A121" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121" s="8" t="s">
         <v>239</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>240</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>10</v>
@@ -3562,13 +3559,13 @@
         <v>62</v>
       </c>
       <c r="E121" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F121" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="F121" s="16" t="s">
+      <c r="G121" s="16" t="s">
         <v>242</v>
-      </c>
-      <c r="G121" s="16" t="s">
-        <v>243</v>
       </c>
       <c r="H121" s="26"/>
     </row>
@@ -3579,19 +3576,19 @@
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
       <c r="F122" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G122" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="G122" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="H122" s="14"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B123" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="B123" s="8" t="s">
-        <v>247</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>10</v>
@@ -3600,10 +3597,10 @@
         <v>25</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>30</v>
@@ -3617,7 +3614,7 @@
       <c r="D124" s="13"/>
       <c r="E124" s="13"/>
       <c r="F124" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G124" s="11" t="s">
         <v>16</v>
@@ -3631,10 +3628,10 @@
       <c r="D125" s="13"/>
       <c r="E125" s="13"/>
       <c r="F125" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G125" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="G125" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="H125" s="13"/>
     </row>
@@ -3645,7 +3642,7 @@
       <c r="D126" s="13"/>
       <c r="E126" s="13"/>
       <c r="F126" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G126" s="11" t="s">
         <v>98</v>
@@ -3659,10 +3656,10 @@
       <c r="D127" s="13"/>
       <c r="E127" s="13"/>
       <c r="F127" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G127" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="G127" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="H127" s="13"/>
     </row>
@@ -3687,10 +3684,10 @@
       <c r="D129" s="13"/>
       <c r="E129" s="13"/>
       <c r="F129" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H129" s="13"/>
     </row>
@@ -3701,19 +3698,19 @@
       <c r="D130" s="14"/>
       <c r="E130" s="14"/>
       <c r="F130" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G130" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="G130" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="H130" s="14"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B131" s="8" t="s">
         <v>258</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>259</v>
       </c>
       <c r="C131" s="9" t="s">
         <v>10</v>
@@ -3722,10 +3719,10 @@
         <v>25</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G131" s="11" t="s">
         <v>14</v>
@@ -3739,7 +3736,7 @@
       <c r="D132" s="13"/>
       <c r="E132" s="13"/>
       <c r="F132" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G132" s="11" t="s">
         <v>16</v>
@@ -3753,10 +3750,10 @@
       <c r="D133" s="13"/>
       <c r="E133" s="13"/>
       <c r="F133" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G133" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="G133" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="H133" s="13"/>
     </row>
@@ -3767,7 +3764,7 @@
       <c r="D134" s="13"/>
       <c r="E134" s="13"/>
       <c r="F134" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G134" s="11" t="s">
         <v>98</v>
@@ -3781,10 +3778,10 @@
       <c r="D135" s="13"/>
       <c r="E135" s="13"/>
       <c r="F135" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G135" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="G135" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="H135" s="13"/>
     </row>
@@ -3809,10 +3806,10 @@
       <c r="D137" s="13"/>
       <c r="E137" s="13"/>
       <c r="F137" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G137" s="11" t="s">
         <v>261</v>
-      </c>
-      <c r="G137" s="11" t="s">
-        <v>262</v>
       </c>
       <c r="H137" s="13"/>
     </row>
@@ -3823,10 +3820,10 @@
       <c r="D138" s="13"/>
       <c r="E138" s="13"/>
       <c r="F138" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G138" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="G138" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="H138" s="13"/>
     </row>
@@ -3860,10 +3857,10 @@
     </row>
     <row r="141">
       <c r="A141" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B141" s="8" t="s">
         <v>263</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>264</v>
       </c>
       <c r="C141" s="9" t="s">
         <v>10</v>
@@ -3872,10 +3869,10 @@
         <v>25</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G141" s="11" t="s">
         <v>14</v>
@@ -3889,7 +3886,7 @@
       <c r="D142" s="13"/>
       <c r="E142" s="13"/>
       <c r="F142" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G142" s="11" t="s">
         <v>16</v>
@@ -3903,10 +3900,10 @@
       <c r="D143" s="13"/>
       <c r="E143" s="13"/>
       <c r="F143" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H143" s="13"/>
     </row>
@@ -3917,10 +3914,10 @@
       <c r="D144" s="13"/>
       <c r="E144" s="13"/>
       <c r="F144" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="G144" s="11" t="s">
         <v>266</v>
-      </c>
-      <c r="G144" s="11" t="s">
-        <v>267</v>
       </c>
       <c r="H144" s="13"/>
     </row>
@@ -3931,10 +3928,10 @@
       <c r="D145" s="13"/>
       <c r="E145" s="13"/>
       <c r="F145" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G145" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H145" s="13"/>
     </row>
@@ -3945,7 +3942,7 @@
       <c r="D146" s="13"/>
       <c r="E146" s="13"/>
       <c r="F146" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G146" s="11" t="s">
         <v>102</v>
@@ -3959,19 +3956,19 @@
       <c r="D147" s="14"/>
       <c r="E147" s="14"/>
       <c r="F147" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="G147" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="G147" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="H147" s="14"/>
     </row>
     <row r="148">
       <c r="A148" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B148" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="B148" s="8" t="s">
-        <v>273</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>10</v>
@@ -3980,10 +3977,10 @@
         <v>25</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G148" s="11" t="s">
         <v>14</v>
@@ -3997,7 +3994,7 @@
       <c r="D149" s="13"/>
       <c r="E149" s="13"/>
       <c r="F149" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G149" s="11" t="s">
         <v>16</v>
@@ -4011,10 +4008,10 @@
       <c r="D150" s="13"/>
       <c r="E150" s="13"/>
       <c r="F150" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G150" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="G150" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="H150" s="13"/>
     </row>
@@ -4025,7 +4022,7 @@
       <c r="D151" s="13"/>
       <c r="E151" s="13"/>
       <c r="F151" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G151" s="11" t="s">
         <v>98</v>
@@ -4039,10 +4036,10 @@
       <c r="D152" s="13"/>
       <c r="E152" s="13"/>
       <c r="F152" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="G152" s="11" t="s">
         <v>275</v>
-      </c>
-      <c r="G152" s="11" t="s">
-        <v>276</v>
       </c>
       <c r="H152" s="13"/>
     </row>
@@ -4053,7 +4050,7 @@
       <c r="D153" s="13"/>
       <c r="E153" s="13"/>
       <c r="F153" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G153" s="11" t="s">
         <v>102</v>
@@ -4067,19 +4064,19 @@
       <c r="D154" s="14"/>
       <c r="E154" s="14"/>
       <c r="F154" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="G154" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="G154" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="H154" s="13"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B155" s="8" t="s">
         <v>277</v>
-      </c>
-      <c r="B155" s="8" t="s">
-        <v>278</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>10</v>
@@ -4088,10 +4085,10 @@
         <v>25</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G155" s="11" t="s">
         <v>14</v>
@@ -4105,7 +4102,7 @@
       <c r="D156" s="13"/>
       <c r="E156" s="13"/>
       <c r="F156" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G156" s="11" t="s">
         <v>32</v>
@@ -4119,10 +4116,10 @@
       <c r="D157" s="13"/>
       <c r="E157" s="13"/>
       <c r="F157" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G157" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="G157" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="H157" s="13"/>
     </row>
@@ -4133,7 +4130,7 @@
       <c r="D158" s="13"/>
       <c r="E158" s="13"/>
       <c r="F158" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G158" s="11" t="s">
         <v>98</v>
@@ -4147,10 +4144,10 @@
       <c r="D159" s="13"/>
       <c r="E159" s="13"/>
       <c r="F159" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G159" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="G159" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="H159" s="13"/>
     </row>
@@ -4175,10 +4172,10 @@
       <c r="D161" s="13"/>
       <c r="E161" s="13"/>
       <c r="F161" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G161" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H161" s="13"/>
     </row>
@@ -4189,19 +4186,19 @@
       <c r="D162" s="14"/>
       <c r="E162" s="14"/>
       <c r="F162" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G162" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="G162" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="H162" s="14"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B163" s="8" t="s">
         <v>280</v>
-      </c>
-      <c r="B163" s="8" t="s">
-        <v>281</v>
       </c>
       <c r="C163" s="9" t="s">
         <v>10</v>
@@ -4210,10 +4207,10 @@
         <v>62</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G163" s="11" t="s">
         <v>30</v>
@@ -4227,7 +4224,7 @@
       <c r="D164" s="13"/>
       <c r="E164" s="13"/>
       <c r="F164" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G164" s="11" t="s">
         <v>32</v>
@@ -4241,10 +4238,10 @@
       <c r="D165" s="13"/>
       <c r="E165" s="13"/>
       <c r="F165" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G165" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H165" s="13"/>
     </row>
@@ -4255,10 +4252,10 @@
       <c r="D166" s="13"/>
       <c r="E166" s="13"/>
       <c r="F166" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G166" s="11" t="s">
         <v>282</v>
-      </c>
-      <c r="G166" s="11" t="s">
-        <v>283</v>
       </c>
       <c r="H166" s="13"/>
     </row>
@@ -4269,10 +4266,10 @@
       <c r="D167" s="13"/>
       <c r="E167" s="13"/>
       <c r="F167" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G167" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H167" s="13"/>
     </row>
@@ -4283,19 +4280,19 @@
       <c r="D168" s="14"/>
       <c r="E168" s="14"/>
       <c r="F168" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="G168" s="11" t="s">
         <v>285</v>
-      </c>
-      <c r="G168" s="11" t="s">
-        <v>286</v>
       </c>
       <c r="H168" s="14"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B169" s="8" t="s">
         <v>287</v>
-      </c>
-      <c r="B169" s="8" t="s">
-        <v>288</v>
       </c>
       <c r="C169" s="9" t="s">
         <v>10</v>
@@ -4304,13 +4301,13 @@
         <v>62</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G169" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H169" s="26"/>
     </row>
@@ -4321,7 +4318,7 @@
       <c r="D170" s="13"/>
       <c r="E170" s="13"/>
       <c r="F170" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G170" s="11" t="s">
         <v>16</v>
@@ -4335,10 +4332,10 @@
       <c r="D171" s="13"/>
       <c r="E171" s="13"/>
       <c r="F171" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G171" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H171" s="13"/>
     </row>
@@ -4349,7 +4346,7 @@
       <c r="D172" s="13"/>
       <c r="E172" s="13"/>
       <c r="F172" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G172" s="11" t="s">
         <v>98</v>
@@ -4363,10 +4360,10 @@
       <c r="D173" s="13"/>
       <c r="E173" s="13"/>
       <c r="F173" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G173" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="G173" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="H173" s="13"/>
     </row>
@@ -4391,10 +4388,10 @@
       <c r="D175" s="13"/>
       <c r="E175" s="13"/>
       <c r="F175" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G175" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H175" s="13"/>
     </row>
@@ -4405,19 +4402,19 @@
       <c r="D176" s="14"/>
       <c r="E176" s="14"/>
       <c r="F176" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G176" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H176" s="14"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B177" s="8" t="s">
         <v>293</v>
-      </c>
-      <c r="B177" s="8" t="s">
-        <v>294</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>10</v>
@@ -4426,10 +4423,10 @@
         <v>11</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G177" s="11" t="s">
         <v>14</v>
@@ -4443,7 +4440,7 @@
       <c r="D178" s="13"/>
       <c r="E178" s="13"/>
       <c r="F178" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G178" s="11" t="s">
         <v>16</v>
@@ -4457,10 +4454,10 @@
       <c r="D179" s="13"/>
       <c r="E179" s="13"/>
       <c r="F179" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G179" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="G179" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="H179" s="13"/>
     </row>
@@ -4471,7 +4468,7 @@
       <c r="D180" s="13"/>
       <c r="E180" s="13"/>
       <c r="F180" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G180" s="11" t="s">
         <v>98</v>
@@ -4485,10 +4482,10 @@
       <c r="D181" s="13"/>
       <c r="E181" s="13"/>
       <c r="F181" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G181" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="G181" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="H181" s="13"/>
     </row>
@@ -4513,10 +4510,10 @@
       <c r="D183" s="13"/>
       <c r="E183" s="13"/>
       <c r="F183" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G183" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H183" s="13"/>
     </row>
@@ -4527,19 +4524,19 @@
       <c r="D184" s="14"/>
       <c r="E184" s="14"/>
       <c r="F184" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G184" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H184" s="14"/>
     </row>
     <row r="185">
       <c r="A185" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="B185" s="20" t="s">
         <v>298</v>
-      </c>
-      <c r="B185" s="20" t="s">
-        <v>299</v>
       </c>
       <c r="C185" s="29" t="s">
         <v>10</v>
@@ -4548,13 +4545,13 @@
         <v>25</v>
       </c>
       <c r="E185" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="F185" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="F185" s="16" t="s">
+      <c r="G185" s="16" t="s">
         <v>301</v>
-      </c>
-      <c r="G185" s="16" t="s">
-        <v>302</v>
       </c>
       <c r="H185" s="27"/>
     </row>

--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="305">
   <si>
     <t>ID</t>
   </si>
@@ -747,10 +747,13 @@
     <t>TC027</t>
   </si>
   <si>
-    <t>Переход на страницу About</t>
+    <t>Переход на страницу About (проверка элементов)</t>
   </si>
   <si>
     <t>1. Меню открывается, кнопка About активна</t>
+  </si>
+  <si>
+    <t>2. Пользователь переходит на страницу About - видна версия, Privacy Policy, Terms of Use</t>
   </si>
   <si>
     <t>TC028</t>
@@ -790,6 +793,9 @@
     <t>1. Приложение работает и не падает</t>
   </si>
   <si>
+    <t>Пропущен. Проверяется в рамках smoke теста вручную</t>
+  </si>
+  <si>
     <t>2. Отключить мобильные данные</t>
   </si>
   <si>
@@ -862,6 +868,9 @@
   </si>
   <si>
     <t>1. Календарь отображается</t>
+  </si>
+  <si>
+    <t>Пропущен как Low-приоритетный. Проверяется в рамках smoke теста вручную</t>
   </si>
   <si>
     <t>2. Попытаться выбрать вчерашнюю дату</t>
@@ -1174,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1249,8 +1258,6 @@
     <xf borderId="2" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -3131,7 +3138,9 @@
       <c r="G97" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="H97" s="26"/>
+      <c r="H97" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14"/>
@@ -3169,7 +3178,9 @@
       <c r="G99" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="H99" s="26"/>
+      <c r="H99" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="14"/>
@@ -3207,7 +3218,9 @@
       <c r="G101" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="H101" s="26"/>
+      <c r="H101" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="14"/>
@@ -3245,7 +3258,9 @@
       <c r="G103" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="H103" s="26"/>
+      <c r="H103" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="14"/>
@@ -3257,16 +3272,16 @@
         <v>45</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>46</v>
+        <v>207</v>
       </c>
       <c r="H104" s="14"/>
     </row>
     <row r="105">
       <c r="A105" s="18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C105" s="19" t="s">
         <v>10</v>
@@ -3275,22 +3290,24 @@
         <v>25</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="H105" s="27"/>
+        <v>212</v>
+      </c>
+      <c r="H105" s="21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C106" s="19" t="s">
         <v>10</v>
@@ -3299,22 +3316,24 @@
         <v>25</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="H106" s="27"/>
+        <v>212</v>
+      </c>
+      <c r="H106" s="21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>10</v>
@@ -3323,15 +3342,17 @@
         <v>25</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="H107" s="26"/>
+        <v>219</v>
+      </c>
+      <c r="H107" s="22" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="13"/>
@@ -3340,10 +3361,10 @@
       <c r="D108" s="13"/>
       <c r="E108" s="13"/>
       <c r="F108" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G108" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H108" s="13"/>
     </row>
@@ -3354,19 +3375,19 @@
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
       <c r="F109" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H109" s="14"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C110" s="9" t="s">
         <v>10</v>
@@ -3375,15 +3396,17 @@
         <v>25</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="H110" s="26"/>
+        <v>219</v>
+      </c>
+      <c r="H110" s="22" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="13"/>
@@ -3392,10 +3415,10 @@
       <c r="D111" s="13"/>
       <c r="E111" s="13"/>
       <c r="F111" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H111" s="13"/>
     </row>
@@ -3406,19 +3429,19 @@
       <c r="D112" s="14"/>
       <c r="E112" s="14"/>
       <c r="F112" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H112" s="14"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C113" s="9" t="s">
         <v>10</v>
@@ -3427,15 +3450,17 @@
         <v>25</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="H113" s="26"/>
+        <v>219</v>
+      </c>
+      <c r="H113" s="22" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="13"/>
@@ -3444,10 +3469,10 @@
       <c r="D114" s="13"/>
       <c r="E114" s="13"/>
       <c r="F114" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H114" s="13"/>
     </row>
@@ -3461,7 +3486,7 @@
         <v>51</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H115" s="13"/>
     </row>
@@ -3472,19 +3497,19 @@
       <c r="D116" s="14"/>
       <c r="E116" s="14"/>
       <c r="F116" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H116" s="14"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C117" s="9" t="s">
         <v>10</v>
@@ -3493,15 +3518,17 @@
         <v>25</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="H117" s="26"/>
+        <v>219</v>
+      </c>
+      <c r="H117" s="22" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="13"/>
@@ -3510,10 +3537,10 @@
       <c r="D118" s="13"/>
       <c r="E118" s="13"/>
       <c r="F118" s="11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H118" s="13"/>
     </row>
@@ -3527,7 +3554,7 @@
         <v>51</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H119" s="13"/>
     </row>
@@ -3538,19 +3565,19 @@
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
       <c r="F120" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H120" s="14"/>
     </row>
     <row r="121">
       <c r="A121" s="25" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>10</v>
@@ -3559,36 +3586,38 @@
         <v>62</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F121" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="H121" s="26"/>
-    </row>
-    <row r="122">
+        <v>244</v>
+      </c>
+      <c r="H121" s="22" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="122" ht="108.0" customHeight="1">
       <c r="A122" s="14"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
       <c r="F122" s="16" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G122" s="16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H122" s="14"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>10</v>
@@ -3597,15 +3626,17 @@
         <v>25</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H123" s="26"/>
+      <c r="H123" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="13"/>
@@ -3614,7 +3645,7 @@
       <c r="D124" s="13"/>
       <c r="E124" s="13"/>
       <c r="F124" s="11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G124" s="11" t="s">
         <v>16</v>
@@ -3628,10 +3659,10 @@
       <c r="D125" s="13"/>
       <c r="E125" s="13"/>
       <c r="F125" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H125" s="13"/>
     </row>
@@ -3642,7 +3673,7 @@
       <c r="D126" s="13"/>
       <c r="E126" s="13"/>
       <c r="F126" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G126" s="11" t="s">
         <v>98</v>
@@ -3656,10 +3687,10 @@
       <c r="D127" s="13"/>
       <c r="E127" s="13"/>
       <c r="F127" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H127" s="13"/>
     </row>
@@ -3684,7 +3715,7 @@
       <c r="D129" s="13"/>
       <c r="E129" s="13"/>
       <c r="F129" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G129" s="11" t="s">
         <v>147</v>
@@ -3698,19 +3729,19 @@
       <c r="D130" s="14"/>
       <c r="E130" s="14"/>
       <c r="F130" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H130" s="14"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C131" s="9" t="s">
         <v>10</v>
@@ -3719,15 +3750,17 @@
         <v>25</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G131" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H131" s="26"/>
+      <c r="H131" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="13"/>
@@ -3736,7 +3769,7 @@
       <c r="D132" s="13"/>
       <c r="E132" s="13"/>
       <c r="F132" s="11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G132" s="11" t="s">
         <v>16</v>
@@ -3750,10 +3783,10 @@
       <c r="D133" s="13"/>
       <c r="E133" s="13"/>
       <c r="F133" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H133" s="13"/>
     </row>
@@ -3764,7 +3797,7 @@
       <c r="D134" s="13"/>
       <c r="E134" s="13"/>
       <c r="F134" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G134" s="11" t="s">
         <v>98</v>
@@ -3778,10 +3811,10 @@
       <c r="D135" s="13"/>
       <c r="E135" s="13"/>
       <c r="F135" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H135" s="13"/>
     </row>
@@ -3806,10 +3839,10 @@
       <c r="D137" s="13"/>
       <c r="E137" s="13"/>
       <c r="F137" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G137" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H137" s="13"/>
     </row>
@@ -3820,10 +3853,10 @@
       <c r="D138" s="13"/>
       <c r="E138" s="13"/>
       <c r="F138" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G138" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H138" s="13"/>
     </row>
@@ -3833,10 +3866,10 @@
       <c r="C139" s="13"/>
       <c r="D139" s="13"/>
       <c r="E139" s="13"/>
-      <c r="F139" s="28">
+      <c r="F139" s="26">
         <v>9.0</v>
       </c>
-      <c r="G139" s="28">
+      <c r="G139" s="26">
         <v>9.0</v>
       </c>
       <c r="H139" s="13"/>
@@ -3847,20 +3880,20 @@
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
       <c r="E140" s="14"/>
-      <c r="F140" s="28">
+      <c r="F140" s="26">
         <v>10.0</v>
       </c>
-      <c r="G140" s="28">
+      <c r="G140" s="26">
         <v>10.0</v>
       </c>
       <c r="H140" s="14"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C141" s="9" t="s">
         <v>10</v>
@@ -3869,15 +3902,17 @@
         <v>25</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G141" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H141" s="26"/>
+      <c r="H141" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="13"/>
@@ -3886,7 +3921,7 @@
       <c r="D142" s="13"/>
       <c r="E142" s="13"/>
       <c r="F142" s="11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G142" s="11" t="s">
         <v>16</v>
@@ -3900,7 +3935,7 @@
       <c r="D143" s="13"/>
       <c r="E143" s="13"/>
       <c r="F143" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G143" s="11" t="s">
         <v>134</v>
@@ -3914,10 +3949,10 @@
       <c r="D144" s="13"/>
       <c r="E144" s="13"/>
       <c r="F144" s="11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H144" s="13"/>
     </row>
@@ -3928,7 +3963,7 @@
       <c r="D145" s="13"/>
       <c r="E145" s="13"/>
       <c r="F145" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G145" s="11" t="s">
         <v>143</v>
@@ -3942,7 +3977,7 @@
       <c r="D146" s="13"/>
       <c r="E146" s="13"/>
       <c r="F146" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G146" s="11" t="s">
         <v>102</v>
@@ -3956,19 +3991,19 @@
       <c r="D147" s="14"/>
       <c r="E147" s="14"/>
       <c r="F147" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G147" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H147" s="14"/>
     </row>
     <row r="148">
       <c r="A148" s="8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>10</v>
@@ -3977,15 +4012,17 @@
         <v>25</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G148" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H148" s="26"/>
+      <c r="H148" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="13"/>
@@ -3994,7 +4031,7 @@
       <c r="D149" s="13"/>
       <c r="E149" s="13"/>
       <c r="F149" s="11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G149" s="11" t="s">
         <v>16</v>
@@ -4008,10 +4045,10 @@
       <c r="D150" s="13"/>
       <c r="E150" s="13"/>
       <c r="F150" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G150" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H150" s="13"/>
     </row>
@@ -4022,7 +4059,7 @@
       <c r="D151" s="13"/>
       <c r="E151" s="13"/>
       <c r="F151" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G151" s="11" t="s">
         <v>98</v>
@@ -4036,10 +4073,10 @@
       <c r="D152" s="13"/>
       <c r="E152" s="13"/>
       <c r="F152" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H152" s="13"/>
     </row>
@@ -4050,7 +4087,7 @@
       <c r="D153" s="13"/>
       <c r="E153" s="13"/>
       <c r="F153" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G153" s="11" t="s">
         <v>102</v>
@@ -4064,19 +4101,19 @@
       <c r="D154" s="14"/>
       <c r="E154" s="14"/>
       <c r="F154" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G154" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H154" s="13"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>10</v>
@@ -4085,10 +4122,10 @@
         <v>25</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G155" s="11" t="s">
         <v>14</v>
@@ -4102,7 +4139,7 @@
       <c r="D156" s="13"/>
       <c r="E156" s="13"/>
       <c r="F156" s="11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G156" s="11" t="s">
         <v>32</v>
@@ -4116,10 +4153,10 @@
       <c r="D157" s="13"/>
       <c r="E157" s="13"/>
       <c r="F157" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G157" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H157" s="13"/>
     </row>
@@ -4130,7 +4167,7 @@
       <c r="D158" s="13"/>
       <c r="E158" s="13"/>
       <c r="F158" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G158" s="11" t="s">
         <v>98</v>
@@ -4144,10 +4181,10 @@
       <c r="D159" s="13"/>
       <c r="E159" s="13"/>
       <c r="F159" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G159" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H159" s="13"/>
     </row>
@@ -4172,7 +4209,7 @@
       <c r="D161" s="13"/>
       <c r="E161" s="13"/>
       <c r="F161" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G161" s="11" t="s">
         <v>147</v>
@@ -4186,19 +4223,19 @@
       <c r="D162" s="14"/>
       <c r="E162" s="14"/>
       <c r="F162" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G162" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H162" s="14"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C163" s="9" t="s">
         <v>10</v>
@@ -4207,15 +4244,17 @@
         <v>62</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G163" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H163" s="26"/>
+      <c r="H163" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="13"/>
@@ -4224,7 +4263,7 @@
       <c r="D164" s="13"/>
       <c r="E164" s="13"/>
       <c r="F164" s="11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G164" s="11" t="s">
         <v>32</v>
@@ -4238,7 +4277,7 @@
       <c r="D165" s="13"/>
       <c r="E165" s="13"/>
       <c r="F165" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G165" s="11" t="s">
         <v>134</v>
@@ -4252,10 +4291,10 @@
       <c r="D166" s="13"/>
       <c r="E166" s="13"/>
       <c r="F166" s="11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G166" s="11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H166" s="13"/>
     </row>
@@ -4266,10 +4305,10 @@
       <c r="D167" s="13"/>
       <c r="E167" s="13"/>
       <c r="F167" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G167" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H167" s="13"/>
     </row>
@@ -4280,19 +4319,19 @@
       <c r="D168" s="14"/>
       <c r="E168" s="14"/>
       <c r="F168" s="11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G168" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H168" s="14"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C169" s="9" t="s">
         <v>10</v>
@@ -4301,15 +4340,17 @@
         <v>62</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G169" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="H169" s="26"/>
+        <v>291</v>
+      </c>
+      <c r="H169" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="13"/>
@@ -4318,7 +4359,7 @@
       <c r="D170" s="13"/>
       <c r="E170" s="13"/>
       <c r="F170" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G170" s="11" t="s">
         <v>16</v>
@@ -4332,10 +4373,10 @@
       <c r="D171" s="13"/>
       <c r="E171" s="13"/>
       <c r="F171" s="11" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G171" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H171" s="13"/>
     </row>
@@ -4346,7 +4387,7 @@
       <c r="D172" s="13"/>
       <c r="E172" s="13"/>
       <c r="F172" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G172" s="11" t="s">
         <v>98</v>
@@ -4360,10 +4401,10 @@
       <c r="D173" s="13"/>
       <c r="E173" s="13"/>
       <c r="F173" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G173" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H173" s="13"/>
     </row>
@@ -4388,7 +4429,7 @@
       <c r="D175" s="13"/>
       <c r="E175" s="13"/>
       <c r="F175" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G175" s="11" t="s">
         <v>147</v>
@@ -4402,19 +4443,19 @@
       <c r="D176" s="14"/>
       <c r="E176" s="14"/>
       <c r="F176" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G176" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H176" s="14"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>10</v>
@@ -4423,15 +4464,17 @@
         <v>11</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G177" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H177" s="26"/>
+      <c r="H177" s="12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="13"/>
@@ -4440,7 +4483,7 @@
       <c r="D178" s="13"/>
       <c r="E178" s="13"/>
       <c r="F178" s="11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G178" s="11" t="s">
         <v>16</v>
@@ -4454,10 +4497,10 @@
       <c r="D179" s="13"/>
       <c r="E179" s="13"/>
       <c r="F179" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G179" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H179" s="13"/>
     </row>
@@ -4468,7 +4511,7 @@
       <c r="D180" s="13"/>
       <c r="E180" s="13"/>
       <c r="F180" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G180" s="11" t="s">
         <v>98</v>
@@ -4482,10 +4525,10 @@
       <c r="D181" s="13"/>
       <c r="E181" s="13"/>
       <c r="F181" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G181" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H181" s="13"/>
     </row>
@@ -4510,7 +4553,7 @@
       <c r="D183" s="13"/>
       <c r="E183" s="13"/>
       <c r="F183" s="11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G183" s="11" t="s">
         <v>147</v>
@@ -4524,36 +4567,38 @@
       <c r="D184" s="14"/>
       <c r="E184" s="14"/>
       <c r="F184" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G184" s="11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H184" s="14"/>
     </row>
     <row r="185">
       <c r="A185" s="20" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B185" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="C185" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="C185" s="27" t="s">
         <v>10</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>25</v>
       </c>
       <c r="E185" s="20" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F185" s="16" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G185" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="H185" s="27"/>
+        <v>304</v>
+      </c>
+      <c r="H185" s="21" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="227">
